--- a/开发设计/字段对应关系.xlsx
+++ b/开发设计/字段对应关系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="14780"/>
+    <workbookView windowWidth="18240" windowHeight="8360" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="全额交易查询" sheetId="10" r:id="rId1"/>
@@ -1927,7 +1927,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2125,9 +2125,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2311,8 +2308,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7606030" y="822325"/>
-          <a:ext cx="110490" cy="400050"/>
+          <a:off x="8255635" y="711200"/>
+          <a:ext cx="110490" cy="366395"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2350,8 +2347,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7580630" y="1029335"/>
-          <a:ext cx="114300" cy="184150"/>
+          <a:off x="8230235" y="918210"/>
+          <a:ext cx="114300" cy="150495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2394,8 +2391,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="23390225"/>
-          <a:ext cx="114300" cy="184150"/>
+          <a:off x="0" y="19816445"/>
+          <a:ext cx="114300" cy="150495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2433,8 +2430,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="23390225"/>
-          <a:ext cx="114300" cy="184150"/>
+          <a:off x="0" y="19816445"/>
+          <a:ext cx="114300" cy="150495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2472,8 +2469,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="23606125"/>
-          <a:ext cx="110490" cy="188595"/>
+          <a:off x="0" y="19998690"/>
+          <a:ext cx="110490" cy="154940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2511,8 +2508,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="23606125"/>
-          <a:ext cx="110490" cy="188595"/>
+          <a:off x="0" y="19998690"/>
+          <a:ext cx="110490" cy="154940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2779,16 +2776,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="73" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="72" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:5">
+    <row r="1" ht="20.65" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2805,16 +2802,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:5">
-      <c r="A2" s="74" t="s">
+    <row r="2" ht="17.65" spans="1:5">
+      <c r="A2" s="73" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:5">
+    <row r="3" ht="14.35" spans="1:5">
       <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="68" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="30" t="s">
@@ -2823,9 +2820,9 @@
       <c r="D3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="75"/>
-    </row>
-    <row r="4" ht="51" spans="1:5">
+      <c r="E3" s="74"/>
+    </row>
+    <row r="4" ht="43" spans="1:5">
       <c r="A4" s="45" t="s">
         <v>10</v>
       </c>
@@ -2842,7 +2839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="34" spans="1:5">
+    <row r="5" ht="28.65" spans="1:5">
       <c r="A5" s="45" t="s">
         <v>14</v>
       </c>
@@ -2859,11 +2856,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:5">
+    <row r="6" ht="14.35" spans="1:5">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="68" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="30" t="s">
@@ -2872,16 +2869,16 @@
       <c r="D6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="75"/>
-    </row>
-    <row r="7" ht="68" spans="1:5">
+      <c r="E6" s="74"/>
+    </row>
+    <row r="7" ht="57.35" spans="1:5">
       <c r="A7" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="76" t="s">
+      <c r="C7" s="75" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="30" t="s">
@@ -2891,11 +2888,11 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:5">
+    <row r="8" ht="14.35" spans="1:5">
       <c r="A8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="68" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="30" t="s">
@@ -2904,13 +2901,13 @@
       <c r="D8" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="75"/>
-    </row>
-    <row r="9" ht="17" spans="1:5">
+      <c r="E8" s="74"/>
+    </row>
+    <row r="9" ht="14.35" spans="1:5">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="68" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -2919,11 +2916,11 @@
       <c r="D9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="76" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:5">
+    <row r="10" ht="14.35" spans="1:5">
       <c r="A10" s="17" t="s">
         <v>29</v>
       </c>
@@ -2936,13 +2933,13 @@
       <c r="D10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="75"/>
-    </row>
-    <row r="11" ht="17" spans="1:5">
+      <c r="E10" s="74"/>
+    </row>
+    <row r="11" ht="14.35" spans="1:5">
       <c r="A11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="68" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="17" t="s">
@@ -2951,16 +2948,16 @@
       <c r="D11" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="75"/>
-    </row>
-    <row r="12" ht="68" spans="1:5">
+      <c r="E11" s="74"/>
+    </row>
+    <row r="12" ht="57.35" spans="1:5">
       <c r="A12" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="75" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="30" t="s">
@@ -2970,7 +2967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:5">
+    <row r="13" ht="14.35" spans="1:5">
       <c r="A13" s="17" t="s">
         <v>34</v>
       </c>
@@ -2983,15 +2980,15 @@
       <c r="D13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="77" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:5">
+    <row r="14" ht="14.35" spans="1:5">
       <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="30" t="s">
@@ -3000,9 +2997,9 @@
       <c r="D14" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="75"/>
-    </row>
-    <row r="15" ht="17" spans="1:5">
+      <c r="E14" s="74"/>
+    </row>
+    <row r="15" ht="14.35" spans="1:5">
       <c r="A15" s="17" t="s">
         <v>40</v>
       </c>
@@ -3015,13 +3012,13 @@
       <c r="D15" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="75"/>
-    </row>
-    <row r="16" ht="17" spans="1:5">
+      <c r="E15" s="74"/>
+    </row>
+    <row r="16" ht="14.35" spans="1:5">
       <c r="A16" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="78" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="45" t="s">
@@ -3030,33 +3027,33 @@
       <c r="D16" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="75"/>
-    </row>
-    <row r="18" ht="20.4" spans="1:5">
-      <c r="A18" s="74" t="s">
+      <c r="E16" s="74"/>
+    </row>
+    <row r="18" ht="17.65" spans="1:5">
+      <c r="A18" s="73" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:5">
+    <row r="19" ht="14.35" spans="1:5">
       <c r="A19" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="79" t="s">
         <v>47</v>
       </c>
       <c r="C19" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="81" t="s">
+      <c r="D19" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="40"/>
     </row>
-    <row r="20" ht="17" spans="1:5">
+    <row r="20" ht="14.35" spans="1:5">
       <c r="A20" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="68" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="30" t="s">
@@ -3067,11 +3064,11 @@
       </c>
       <c r="E20" s="40"/>
     </row>
-    <row r="21" ht="17" spans="1:5">
+    <row r="21" ht="14.35" spans="1:5">
       <c r="A21" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="68" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="30" t="s">
@@ -3082,11 +3079,11 @@
       </c>
       <c r="E21" s="40"/>
     </row>
-    <row r="22" ht="17" spans="1:5">
+    <row r="22" ht="14.35" spans="1:5">
       <c r="A22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="68" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="30" t="s">
@@ -3095,41 +3092,41 @@
       <c r="D22" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="77" t="s">
+      <c r="E22" s="76" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:5">
+    <row r="23" ht="14.35" spans="1:5">
       <c r="A23" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="82" t="s">
+      <c r="B23" s="79"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="81" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" ht="17" spans="1:5">
+    <row r="24" ht="14.35" spans="1:5">
       <c r="A24" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="79" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="81" t="s">
+      <c r="D24" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="40"/>
     </row>
-    <row r="25" ht="17" spans="1:5">
+    <row r="25" ht="14.35" spans="1:5">
       <c r="A25" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="30" t="s">
@@ -3140,156 +3137,156 @@
       </c>
       <c r="E25" s="40"/>
     </row>
-    <row r="26" ht="17" spans="1:5">
+    <row r="26" ht="14.35" spans="1:5">
       <c r="A26" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="80" t="s">
+      <c r="B26" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="83" t="s">
+      <c r="C26" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="81" t="s">
+      <c r="D26" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="40"/>
     </row>
-    <row r="27" ht="17" spans="1:5">
+    <row r="27" ht="14.35" spans="1:5">
       <c r="A27" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="81" t="s">
+      <c r="D27" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E27" s="40"/>
     </row>
-    <row r="28" ht="17" spans="1:5">
+    <row r="28" ht="14.35" spans="1:5">
       <c r="A28" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C28" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="81" t="s">
+      <c r="D28" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="84" t="s">
+      <c r="E28" s="83" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" ht="17" spans="1:5">
+    <row r="29" ht="14.35" spans="1:5">
       <c r="A29" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="83" t="s">
+      <c r="B29" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="81" t="s">
+      <c r="D29" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="84" t="s">
+      <c r="E29" s="83" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="30" ht="17" spans="1:5">
-      <c r="A30" s="85" t="s">
+    <row r="30" ht="14.35" spans="1:5">
+      <c r="A30" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="80" t="s">
+      <c r="B30" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="81" t="s">
+      <c r="C30" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="81" t="s">
+      <c r="D30" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E30" s="40"/>
     </row>
-    <row r="31" ht="17" spans="1:5">
-      <c r="A31" s="85" t="s">
+    <row r="31" ht="14.35" spans="1:5">
+      <c r="A31" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="80" t="s">
+      <c r="B31" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="81" t="s">
+      <c r="C31" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="81" t="s">
+      <c r="D31" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="50"/>
     </row>
-    <row r="33" ht="20.4" spans="1:5">
+    <row r="33" ht="17.65" spans="1:5">
       <c r="A33" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" ht="17" spans="1:5">
-      <c r="A34" s="85" t="s">
+    <row r="34" ht="14.35" spans="1:5">
+      <c r="A34" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="80" t="s">
+      <c r="B34" s="79" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="81" t="s">
+      <c r="D34" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="50"/>
     </row>
-    <row r="35" ht="17" spans="1:5">
-      <c r="A35" s="85" t="s">
+    <row r="35" ht="14.35" spans="1:5">
+      <c r="A35" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="86" t="s">
+      <c r="B35" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="81" t="s">
+      <c r="D35" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="88" t="s">
+      <c r="E35" s="87" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="36" ht="17" spans="1:5">
-      <c r="A36" s="85" t="s">
+    <row r="36" ht="14.35" spans="1:5">
+      <c r="A36" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="86" t="s">
+      <c r="B36" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="81" t="s">
+      <c r="D36" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="88" t="s">
+      <c r="E36" s="87" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="37" ht="17" spans="1:5">
-      <c r="A37" s="85" t="s">
+    <row r="37" ht="14.35" spans="1:5">
+      <c r="A37" s="84" t="s">
         <v>34</v>
       </c>
       <c r="B37" s="21" t="s">
@@ -3301,171 +3298,171 @@
       <c r="D37" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="78" t="s">
+      <c r="E37" s="77" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="17" spans="1:5">
-      <c r="A38" s="85" t="s">
+    <row r="38" ht="14.35" spans="1:5">
+      <c r="A38" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="89" t="s">
+      <c r="B38" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="85" t="s">
+      <c r="C38" s="84" t="s">
         <v>79</v>
       </c>
-      <c r="D38" s="81" t="s">
+      <c r="D38" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="50"/>
     </row>
-    <row r="39" ht="17" spans="1:5">
-      <c r="A39" s="85" t="s">
+    <row r="39" ht="14.35" spans="1:5">
+      <c r="A39" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="86" t="s">
+      <c r="B39" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="87" t="s">
+      <c r="C39" s="86" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="81" t="s">
+      <c r="D39" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E39" s="50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="40" ht="17" spans="1:5">
-      <c r="A40" s="85" t="s">
+    <row r="40" ht="14.35" spans="1:5">
+      <c r="A40" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="90" t="s">
+      <c r="B40" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="85" t="s">
+      <c r="C40" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="D40" s="81" t="s">
+      <c r="D40" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="41" ht="17" spans="1:5">
-      <c r="A41" s="85" t="s">
+    <row r="41" ht="14.35" spans="1:5">
+      <c r="A41" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="86" t="s">
+      <c r="B41" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="87" t="s">
+      <c r="C41" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="D41" s="81" t="s">
+      <c r="D41" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="50"/>
     </row>
-    <row r="42" ht="17" spans="1:5">
-      <c r="A42" s="85" t="s">
+    <row r="42" ht="14.35" spans="1:5">
+      <c r="A42" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="80" t="s">
+      <c r="B42" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="81" t="s">
+      <c r="C42" s="80" t="s">
         <v>57</v>
       </c>
-      <c r="D42" s="81" t="s">
+      <c r="D42" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="50"/>
     </row>
-    <row r="43" ht="17" spans="1:5">
-      <c r="A43" s="85" t="s">
+    <row r="43" ht="14.35" spans="1:5">
+      <c r="A43" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="89" t="s">
+      <c r="B43" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="85" t="s">
+      <c r="C43" s="84" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="81" t="s">
+      <c r="D43" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="50"/>
     </row>
-    <row r="44" ht="17" spans="1:5">
-      <c r="A44" s="85" t="s">
+    <row r="44" ht="14.35" spans="1:5">
+      <c r="A44" s="84" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="86" t="s">
+      <c r="B44" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="87" t="s">
+      <c r="C44" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="81" t="s">
+      <c r="D44" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E44" s="50"/>
     </row>
-    <row r="45" ht="17" spans="1:5">
-      <c r="A45" s="85" t="s">
+    <row r="45" ht="14.35" spans="1:5">
+      <c r="A45" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="86" t="s">
+      <c r="B45" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="87" t="s">
+      <c r="C45" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="81" t="s">
+      <c r="D45" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E45" s="50"/>
     </row>
-    <row r="46" ht="17" spans="1:5">
-      <c r="A46" s="85" t="s">
+    <row r="46" ht="14.35" spans="1:5">
+      <c r="A46" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="B46" s="83" t="s">
+      <c r="B46" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="83" t="s">
+      <c r="C46" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="D46" s="81" t="s">
+      <c r="D46" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="84" t="s">
+      <c r="E46" s="83" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" ht="17" spans="1:5">
-      <c r="A47" s="85" t="s">
+    <row r="47" ht="14.35" spans="1:5">
+      <c r="A47" s="84" t="s">
         <v>98</v>
       </c>
-      <c r="B47" s="86" t="s">
+      <c r="B47" s="85" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="87" t="s">
+      <c r="C47" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="81" t="s">
+      <c r="D47" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="50"/>
     </row>
-    <row r="48" ht="17" spans="1:5">
-      <c r="A48" s="85" t="s">
+    <row r="48" ht="14.35" spans="1:5">
+      <c r="A48" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="B48" s="69" t="s">
+      <c r="B48" s="68" t="s">
         <v>27</v>
       </c>
       <c r="C48" s="30" t="s">
@@ -3474,45 +3471,45 @@
       <c r="D48" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="77" t="s">
+      <c r="E48" s="76" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="49" ht="17" spans="1:5">
-      <c r="A49" s="85" t="s">
+    <row r="49" ht="14.35" spans="1:5">
+      <c r="A49" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="86" t="s">
+      <c r="B49" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="87" t="s">
+      <c r="C49" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="D49" s="81" t="s">
+      <c r="D49" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E49" s="50"/>
     </row>
-    <row r="50" ht="17" spans="1:5">
-      <c r="A50" s="85" t="s">
+    <row r="50" ht="14.35" spans="1:5">
+      <c r="A50" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="89" t="s">
+      <c r="B50" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="C50" s="85" t="s">
+      <c r="C50" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="81" t="s">
+      <c r="D50" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="50"/>
     </row>
-    <row r="51" ht="17" spans="1:5">
-      <c r="A51" s="85" t="s">
+    <row r="51" ht="14.35" spans="1:5">
+      <c r="A51" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="69" t="s">
+      <c r="B51" s="68" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="30" t="s">
@@ -3523,14 +3520,14 @@
       </c>
       <c r="E51" s="50"/>
     </row>
-    <row r="52" ht="17" spans="1:5">
-      <c r="A52" s="85" t="s">
+    <row r="52" ht="14.35" spans="1:5">
+      <c r="A52" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="89" t="s">
+      <c r="B52" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="85" t="s">
+      <c r="C52" s="84" t="s">
         <v>102</v>
       </c>
       <c r="D52" s="30" t="s">
@@ -3538,8 +3535,8 @@
       </c>
       <c r="E52" s="50"/>
     </row>
-    <row r="53" ht="17" spans="1:5">
-      <c r="A53" s="85" t="s">
+    <row r="53" ht="14.35" spans="1:5">
+      <c r="A53" s="84" t="s">
         <v>29</v>
       </c>
       <c r="B53" s="36" t="s">
@@ -3553,37 +3550,37 @@
       </c>
       <c r="E53" s="50"/>
     </row>
-    <row r="54" ht="17" spans="1:5">
-      <c r="A54" s="85" t="s">
+    <row r="54" ht="14.35" spans="1:5">
+      <c r="A54" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="B54" s="89"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="82" t="s">
+      <c r="B54" s="88"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="84"/>
+      <c r="E54" s="81" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="55" ht="17" spans="1:5">
-      <c r="A55" s="85" t="s">
+    <row r="55" ht="14.35" spans="1:5">
+      <c r="A55" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="89" t="s">
+      <c r="B55" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="C55" s="85" t="s">
+      <c r="C55" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="D55" s="81" t="s">
+      <c r="D55" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="50"/>
     </row>
-    <row r="56" ht="17" spans="1:5">
-      <c r="A56" s="85" t="s">
+    <row r="56" ht="14.35" spans="1:5">
+      <c r="A56" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="69" t="s">
+      <c r="B56" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C56" s="30" t="s">
@@ -3594,8 +3591,8 @@
       </c>
       <c r="E56" s="50"/>
     </row>
-    <row r="57" ht="17" spans="1:5">
-      <c r="A57" s="85" t="s">
+    <row r="57" ht="14.35" spans="1:5">
+      <c r="A57" s="84" t="s">
         <v>40</v>
       </c>
       <c r="B57" s="36" t="s">
@@ -3609,150 +3606,150 @@
       </c>
       <c r="E57" s="50"/>
     </row>
-    <row r="58" ht="17" spans="1:5">
-      <c r="A58" s="85" t="s">
+    <row r="58" ht="14.35" spans="1:5">
+      <c r="A58" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="B58" s="86" t="s">
+      <c r="B58" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="C58" s="87" t="s">
+      <c r="C58" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="D58" s="81" t="s">
+      <c r="D58" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E58" s="50"/>
     </row>
-    <row r="59" ht="17" spans="1:5">
-      <c r="A59" s="85" t="s">
+    <row r="59" ht="14.35" spans="1:5">
+      <c r="A59" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="80" t="s">
+      <c r="B59" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="C59" s="83" t="s">
+      <c r="C59" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="D59" s="81" t="s">
+      <c r="D59" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E59" s="50"/>
     </row>
-    <row r="60" ht="17" spans="1:5">
-      <c r="A60" s="85" t="s">
+    <row r="60" ht="14.35" spans="1:5">
+      <c r="A60" s="84" t="s">
         <v>109</v>
       </c>
-      <c r="B60" s="89" t="s">
+      <c r="B60" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="85" t="s">
+      <c r="C60" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="D60" s="81" t="s">
+      <c r="D60" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="50"/>
     </row>
-    <row r="61" ht="17" spans="1:5">
-      <c r="A61" s="85" t="s">
+    <row r="61" ht="14.35" spans="1:5">
+      <c r="A61" s="84" t="s">
         <v>112</v>
       </c>
-      <c r="B61" s="86" t="s">
+      <c r="B61" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="C61" s="87" t="s">
+      <c r="C61" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="81" t="s">
+      <c r="D61" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E61" s="50"/>
     </row>
-    <row r="62" ht="17" spans="1:5">
-      <c r="A62" s="85" t="s">
+    <row r="62" ht="14.35" spans="1:5">
+      <c r="A62" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="B62" s="86" t="s">
+      <c r="B62" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="C62" s="87" t="s">
+      <c r="C62" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="D62" s="81" t="s">
+      <c r="D62" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E62" s="50"/>
     </row>
-    <row r="63" ht="17" spans="1:5">
-      <c r="A63" s="85" t="s">
+    <row r="63" ht="14.35" spans="1:5">
+      <c r="A63" s="84" t="s">
         <v>58</v>
       </c>
-      <c r="B63" s="83" t="s">
+      <c r="B63" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="C63" s="81" t="s">
+      <c r="C63" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="D63" s="81" t="s">
+      <c r="D63" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="84" t="s">
+      <c r="E63" s="83" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" ht="17" spans="1:5">
-      <c r="A64" s="85" t="s">
+    <row r="64" ht="14.35" spans="1:5">
+      <c r="A64" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="B64" s="86" t="s">
+      <c r="B64" s="85" t="s">
         <v>119</v>
       </c>
-      <c r="C64" s="87" t="s">
+      <c r="C64" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="D64" s="81" t="s">
+      <c r="D64" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E64" s="50"/>
     </row>
-    <row r="65" ht="17" spans="1:5">
-      <c r="A65" s="85" t="s">
+    <row r="65" ht="14.35" spans="1:5">
+      <c r="A65" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="B65" s="89" t="s">
+      <c r="B65" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="C65" s="85" t="s">
+      <c r="C65" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="D65" s="81" t="s">
+      <c r="D65" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="91" t="s">
+      <c r="E65" s="90" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="66" ht="17" spans="1:5">
-      <c r="A66" s="85" t="s">
+    <row r="66" ht="14.35" spans="1:5">
+      <c r="A66" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="B66" s="80" t="s">
+      <c r="B66" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="81" t="s">
+      <c r="C66" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="D66" s="81" t="s">
+      <c r="D66" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E66" s="50"/>
     </row>
-    <row r="67" ht="17" spans="1:5">
-      <c r="A67" s="85" t="s">
+    <row r="67" ht="14.35" spans="1:5">
+      <c r="A67" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B67" s="69" t="s">
+      <c r="B67" s="68" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="30" t="s">
@@ -3763,14 +3760,14 @@
       </c>
       <c r="E67" s="50"/>
     </row>
-    <row r="68" ht="17" spans="1:5">
-      <c r="A68" s="85" t="s">
+    <row r="68" ht="14.35" spans="1:5">
+      <c r="A68" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="B68" s="89" t="s">
+      <c r="B68" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="C68" s="85" t="s">
+      <c r="C68" s="84" t="s">
         <v>125</v>
       </c>
       <c r="D68" s="30" t="s">
@@ -3778,14 +3775,14 @@
       </c>
       <c r="E68" s="50"/>
     </row>
-    <row r="69" ht="17" spans="1:5">
-      <c r="A69" s="85" t="s">
+    <row r="69" ht="14.35" spans="1:5">
+      <c r="A69" s="84" t="s">
         <v>127</v>
       </c>
-      <c r="B69" s="89" t="s">
+      <c r="B69" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="C69" s="85" t="s">
+      <c r="C69" s="84" t="s">
         <v>127</v>
       </c>
       <c r="D69" s="30" t="s">
@@ -3793,11 +3790,11 @@
       </c>
       <c r="E69" s="50"/>
     </row>
-    <row r="70" ht="17" spans="1:5">
-      <c r="A70" s="85" t="s">
+    <row r="70" ht="14.35" spans="1:5">
+      <c r="A70" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="B70" s="79" t="s">
+      <c r="B70" s="78" t="s">
         <v>44</v>
       </c>
       <c r="C70" s="45" t="s">
@@ -3808,44 +3805,44 @@
       </c>
       <c r="E70" s="50"/>
     </row>
-    <row r="71" ht="17" spans="1:5">
-      <c r="A71" s="85" t="s">
+    <row r="71" ht="14.35" spans="1:5">
+      <c r="A71" s="84" t="s">
         <v>129</v>
       </c>
-      <c r="B71" s="86" t="s">
+      <c r="B71" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="C71" s="87" t="s">
+      <c r="C71" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="D71" s="81" t="s">
+      <c r="D71" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E71" s="50"/>
     </row>
-    <row r="72" ht="17" spans="1:5">
-      <c r="A72" s="85" t="s">
+    <row r="72" ht="14.35" spans="1:5">
+      <c r="A72" s="84" t="s">
         <v>132</v>
       </c>
-      <c r="B72" s="90" t="s">
+      <c r="B72" s="89" t="s">
         <v>133</v>
       </c>
-      <c r="C72" s="87" t="s">
+      <c r="C72" s="86" t="s">
         <v>134</v>
       </c>
-      <c r="D72" s="81" t="s">
+      <c r="D72" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E72" s="50"/>
     </row>
-    <row r="73" ht="17" spans="1:5">
-      <c r="A73" s="85" t="s">
+    <row r="73" ht="14.35" spans="1:5">
+      <c r="A73" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="89" t="s">
+      <c r="B73" s="88" t="s">
         <v>136</v>
       </c>
-      <c r="C73" s="85" t="s">
+      <c r="C73" s="84" t="s">
         <v>135</v>
       </c>
       <c r="D73" s="30" t="s">
@@ -3853,44 +3850,44 @@
       </c>
       <c r="E73" s="50"/>
     </row>
-    <row r="74" ht="17" spans="1:5">
-      <c r="A74" s="85" t="s">
+    <row r="74" ht="14.35" spans="1:5">
+      <c r="A74" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="89" t="s">
+      <c r="B74" s="88" t="s">
         <v>138</v>
       </c>
-      <c r="C74" s="85" t="s">
+      <c r="C74" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="81" t="s">
+      <c r="D74" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E74" s="50"/>
     </row>
-    <row r="75" ht="17" spans="1:5">
-      <c r="A75" s="85" t="s">
+    <row r="75" ht="14.35" spans="1:5">
+      <c r="A75" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="B75" s="89" t="s">
+      <c r="B75" s="88" t="s">
         <v>140</v>
       </c>
-      <c r="C75" s="85" t="s">
+      <c r="C75" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="D75" s="81" t="s">
+      <c r="D75" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E75" s="50"/>
     </row>
-    <row r="76" ht="17" spans="1:5">
-      <c r="A76" s="85" t="s">
+    <row r="76" ht="14.35" spans="1:5">
+      <c r="A76" s="84" t="s">
         <v>141</v>
       </c>
-      <c r="B76" s="89" t="s">
+      <c r="B76" s="88" t="s">
         <v>142</v>
       </c>
-      <c r="C76" s="85" t="s">
+      <c r="C76" s="84" t="s">
         <v>141</v>
       </c>
       <c r="D76" s="30" t="s">
@@ -3900,65 +3897,65 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" ht="17" spans="1:5">
-      <c r="A77" s="85" t="s">
+    <row r="77" ht="14.35" spans="1:5">
+      <c r="A77" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="B77" s="89" t="s">
+      <c r="B77" s="88" t="s">
         <v>144</v>
       </c>
-      <c r="C77" s="85" t="s">
+      <c r="C77" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="D77" s="81" t="s">
+      <c r="D77" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E77" s="38"/>
     </row>
-    <row r="78" ht="17" spans="1:5">
-      <c r="A78" s="85" t="s">
+    <row r="78" ht="14.35" spans="1:5">
+      <c r="A78" s="84" t="s">
         <v>145</v>
       </c>
-      <c r="B78" s="89" t="s">
+      <c r="B78" s="88" t="s">
         <v>146</v>
       </c>
-      <c r="C78" s="85" t="s">
+      <c r="C78" s="84" t="s">
         <v>145</v>
       </c>
-      <c r="D78" s="81" t="s">
+      <c r="D78" s="80" t="s">
         <v>9</v>
       </c>
       <c r="E78" s="50" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="80" ht="20.4" spans="1:5">
-      <c r="A80" s="74" t="s">
+    <row r="80" ht="17.65" spans="1:5">
+      <c r="A80" s="73" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="81" ht="17" spans="1:5">
+    <row r="81" ht="14.35" spans="1:5">
       <c r="A81" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="B81" s="90" t="s">
+      <c r="B81" s="89" t="s">
         <v>150</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="D81" s="81" t="s">
+      <c r="D81" s="80" t="s">
         <v>18</v>
       </c>
       <c r="E81" s="48" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="82" ht="17" spans="1:5">
-      <c r="A82" s="92" t="s">
+    <row r="82" ht="14.35" spans="1:5">
+      <c r="A82" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B82" s="69" t="s">
+      <c r="B82" s="68" t="s">
         <v>17</v>
       </c>
       <c r="C82" s="30" t="s">
@@ -3968,25 +3965,25 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" ht="17" spans="1:5">
-      <c r="A83" s="92" t="s">
+    <row r="83" ht="14.35" spans="1:5">
+      <c r="A83" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="B83" s="86" t="s">
+      <c r="B83" s="85" t="s">
         <v>153</v>
       </c>
-      <c r="C83" s="81" t="s">
+      <c r="C83" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="D83" s="81" t="s">
+      <c r="D83" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="84" ht="17" spans="1:5">
-      <c r="A84" s="92" t="s">
+    <row r="84" ht="14.35" spans="1:5">
+      <c r="A84" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="B84" s="69" t="s">
+      <c r="B84" s="68" t="s">
         <v>32</v>
       </c>
       <c r="C84" s="17" t="s">
@@ -3996,100 +3993,100 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" ht="17" spans="1:5">
-      <c r="A85" s="92" t="s">
+    <row r="85" ht="14.35" spans="1:5">
+      <c r="A85" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="B85" s="86" t="s">
+      <c r="B85" s="85" t="s">
         <v>156</v>
       </c>
       <c r="C85" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="D85" s="81" t="s">
+      <c r="D85" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="86" ht="17" spans="1:5">
-      <c r="A86" s="92" t="s">
+    <row r="86" ht="14.35" spans="1:5">
+      <c r="A86" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="B86" s="86" t="s">
+      <c r="B86" s="85" t="s">
         <v>159</v>
       </c>
-      <c r="C86" s="92" t="s">
+      <c r="C86" s="91" t="s">
         <v>160</v>
       </c>
-      <c r="D86" s="81" t="s">
+      <c r="D86" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="87" ht="17" spans="1:5">
-      <c r="A87" s="92" t="s">
+    <row r="87" ht="14.35" spans="1:5">
+      <c r="A87" s="91" t="s">
         <v>161</v>
       </c>
-      <c r="B87" s="86" t="s">
+      <c r="B87" s="85" t="s">
         <v>162</v>
       </c>
-      <c r="C87" s="92" t="s">
+      <c r="C87" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="D87" s="81" t="s">
+      <c r="D87" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" ht="17" spans="1:5">
-      <c r="A88" s="92" t="s">
+    <row r="88" ht="14.35" spans="1:5">
+      <c r="A88" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="B88" s="86" t="s">
+      <c r="B88" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="C88" s="92" t="s">
+      <c r="C88" s="91" t="s">
         <v>166</v>
       </c>
-      <c r="D88" s="81" t="s">
+      <c r="D88" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="89" ht="17" spans="1:5">
-      <c r="A89" s="92" t="s">
+    <row r="89" ht="14.35" spans="1:5">
+      <c r="A89" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="B89" s="90" t="s">
+      <c r="B89" s="89" t="s">
         <v>168</v>
       </c>
-      <c r="C89" s="92" t="s">
+      <c r="C89" s="91" t="s">
         <v>167</v>
       </c>
-      <c r="D89" s="81" t="s">
+      <c r="D89" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="90" ht="17" spans="1:5">
-      <c r="A90" s="92" t="s">
+    <row r="90" ht="14.35" spans="1:5">
+      <c r="A90" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="B90" s="86" t="s">
+      <c r="B90" s="85" t="s">
         <v>170</v>
       </c>
-      <c r="C90" s="92" t="s">
+      <c r="C90" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="D90" s="81" t="s">
+      <c r="D90" s="80" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="92" ht="41" spans="1:5">
-      <c r="A92" s="93" t="s">
+    <row r="92" ht="35.35" spans="1:5">
+      <c r="A92" s="92" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="93" ht="20.4" spans="1:5">
-      <c r="A93" s="94"/>
-    </row>
-    <row r="94" ht="41" spans="1:5">
-      <c r="A94" s="95" t="s">
+    <row r="93" ht="17.65" spans="1:5">
+      <c r="A93" s="93"/>
+    </row>
+    <row r="94" ht="35.35" spans="1:5">
+      <c r="A94" s="94" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4106,19 +4103,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AL96"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" style="60" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="61" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" style="60" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" style="61" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" style="62" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" style="60" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="61" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" style="60" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" style="61" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" style="62" customWidth="1"/>
     <col min="6" max="6" width="9" style="48"/>
-    <col min="7" max="7" width="29.2019230769231" style="48" customWidth="1"/>
+    <col min="7" max="7" width="29.2035398230088" style="48" customWidth="1"/>
     <col min="8" max="16384" width="9" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:38">
+    <row r="1" ht="20.65" spans="1:38">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4135,20 +4132,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:38">
+    <row r="2" ht="17.65" spans="1:38">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="63"/>
       <c r="C2" s="64"/>
       <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
+      <c r="E2" s="53"/>
       <c r="F2" s="35" t="s">
         <v>173</v>
       </c>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" ht="17" spans="1:38">
+    <row r="3" ht="14.35" spans="1:38">
       <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
@@ -4161,7 +4158,7 @@
       <c r="D3" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E3" s="67"/>
+      <c r="E3" s="66"/>
       <c r="F3" s="37"/>
       <c r="G3" s="38" t="s">
         <v>176</v>
@@ -4180,13 +4177,13 @@
       <c r="D4" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E4" s="66"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="39"/>
       <c r="G4" s="40" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:38">
+    <row r="5" ht="14.35" spans="1:38">
       <c r="A5" s="6" t="s">
         <v>72</v>
       </c>
@@ -4199,7 +4196,7 @@
       <c r="D5" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E5" s="66" t="s">
+      <c r="E5" s="53" t="s">
         <v>74</v>
       </c>
       <c r="F5" s="42"/>
@@ -4207,7 +4204,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" ht="51" spans="1:38">
+    <row r="6" ht="43" spans="1:38">
       <c r="A6" s="45" t="s">
         <v>10</v>
       </c>
@@ -4220,11 +4217,11 @@
       <c r="D6" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="67" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="34" spans="1:38">
+    <row r="7" ht="28.65" spans="1:38">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
@@ -4237,11 +4234,11 @@
       <c r="D7" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="66" t="s">
+      <c r="E7" s="53" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:38">
+    <row r="8" ht="14.35" spans="1:38">
       <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
@@ -4254,11 +4251,11 @@
       <c r="D8" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="66" t="s">
+      <c r="E8" s="53" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:38">
+    <row r="9" ht="14.35" spans="1:38">
       <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
@@ -4268,12 +4265,12 @@
       <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="66"/>
-    </row>
-    <row r="10" ht="17" spans="1:38">
+      <c r="E9" s="53"/>
+    </row>
+    <row r="10" ht="14.35" spans="1:38">
       <c r="A10" s="6" t="s">
         <v>31</v>
       </c>
@@ -4283,12 +4280,12 @@
       <c r="C10" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="69" t="s">
+      <c r="D10" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="66"/>
-    </row>
-    <row r="11" ht="17" spans="1:38">
+      <c r="E10" s="53"/>
+    </row>
+    <row r="11" ht="14.35" spans="1:38">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
@@ -4301,9 +4298,9 @@
       <c r="D11" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E11" s="66"/>
-    </row>
-    <row r="12" ht="17" spans="1:38">
+      <c r="E11" s="53"/>
+    </row>
+    <row r="12" ht="14.35" spans="1:38">
       <c r="A12" s="6" t="s">
         <v>180</v>
       </c>
@@ -4316,25 +4313,25 @@
       <c r="D12" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E12" s="66"/>
+      <c r="E12" s="53"/>
     </row>
     <row r="13" spans="1:38">
       <c r="A13" s="6"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="66"/>
-    </row>
-    <row r="14" ht="20.4" spans="1:38">
+      <c r="E13" s="53"/>
+    </row>
+    <row r="14" ht="17.65" spans="1:38">
       <c r="A14" s="33" t="s">
         <v>45</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
       <c r="D14" s="21"/>
-      <c r="E14" s="66"/>
-    </row>
-    <row r="15" ht="17" spans="1:38">
+      <c r="E14" s="53"/>
+    </row>
+    <row r="15" ht="14.35" spans="1:38">
       <c r="A15" s="30" t="s">
         <v>46</v>
       </c>
@@ -4347,42 +4344,42 @@
       <c r="D15" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E15" s="70"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="71"/>
-      <c r="W15" s="71"/>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="71"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="71"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
-      <c r="AD15" s="71"/>
-      <c r="AE15" s="71"/>
-      <c r="AF15" s="71"/>
-      <c r="AG15" s="71"/>
-      <c r="AH15" s="71"/>
-      <c r="AI15" s="71"/>
-      <c r="AJ15" s="71"/>
-      <c r="AK15" s="71"/>
-      <c r="AL15" s="71"/>
-    </row>
-    <row r="16" ht="17" spans="1:38">
+      <c r="E15" s="69"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="70"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+      <c r="Z15" s="70"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="70"/>
+      <c r="AC15" s="70"/>
+      <c r="AD15" s="70"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+      <c r="AI15" s="70"/>
+      <c r="AJ15" s="70"/>
+      <c r="AK15" s="70"/>
+      <c r="AL15" s="70"/>
+    </row>
+    <row r="16" ht="14.35" spans="1:38">
       <c r="A16" s="30" t="s">
         <v>23</v>
       </c>
@@ -4395,9 +4392,9 @@
       <c r="D16" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E16" s="66"/>
-    </row>
-    <row r="17" ht="17" spans="1:5">
+      <c r="E16" s="53"/>
+    </row>
+    <row r="17" ht="14.35" spans="1:5">
       <c r="A17" s="30" t="s">
         <v>6</v>
       </c>
@@ -4410,9 +4407,9 @@
       <c r="D17" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E17" s="66"/>
-    </row>
-    <row r="18" ht="17" spans="1:5">
+      <c r="E17" s="53"/>
+    </row>
+    <row r="18" ht="14.35" spans="1:5">
       <c r="A18" s="30" t="s">
         <v>26</v>
       </c>
@@ -4425,11 +4422,11 @@
       <c r="D18" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="53" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:5">
+    <row r="19" ht="14.35" spans="1:5">
       <c r="A19" s="30" t="s">
         <v>50</v>
       </c>
@@ -4442,9 +4439,9 @@
       <c r="D19" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E19" s="66"/>
-    </row>
-    <row r="20" ht="17" spans="1:5">
+      <c r="E19" s="53"/>
+    </row>
+    <row r="20" ht="14.35" spans="1:5">
       <c r="A20" s="30" t="s">
         <v>75</v>
       </c>
@@ -4461,7 +4458,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="1:5">
+    <row r="21" ht="14.35" spans="1:5">
       <c r="A21" s="30" t="s">
         <v>72</v>
       </c>
@@ -4474,11 +4471,11 @@
       <c r="D21" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E21" s="66" t="s">
+      <c r="E21" s="53" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="1:5">
+    <row r="22" ht="14.35" spans="1:5">
       <c r="A22" s="30" t="s">
         <v>29</v>
       </c>
@@ -4492,7 +4489,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:5">
+    <row r="23" ht="14.35" spans="1:5">
       <c r="A23" s="30" t="s">
         <v>182</v>
       </c>
@@ -4509,7 +4506,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" ht="17" spans="1:5">
+    <row r="24" ht="14.35" spans="1:5">
       <c r="A24" s="30" t="s">
         <v>185</v>
       </c>
@@ -4526,7 +4523,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="1:5">
+    <row r="25" ht="14.35" spans="1:5">
       <c r="A25" s="30" t="s">
         <v>43</v>
       </c>
@@ -4540,7 +4537,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" ht="17" spans="1:5">
+    <row r="26" ht="14.35" spans="1:5">
       <c r="A26" s="6" t="s">
         <v>180</v>
       </c>
@@ -4554,7 +4551,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" ht="17" spans="1:5">
+    <row r="27" ht="14.35" spans="1:5">
       <c r="A27" s="6" t="s">
         <v>188</v>
       </c>
@@ -4571,7 +4568,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" ht="17" spans="1:5">
+    <row r="28" ht="14.35" spans="1:5">
       <c r="A28" s="30" t="s">
         <v>189</v>
       </c>
@@ -4585,7 +4582,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" ht="17" spans="1:5">
+    <row r="29" ht="14.35" spans="1:5">
       <c r="A29" s="30" t="s">
         <v>192</v>
       </c>
@@ -4599,7 +4596,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" ht="17" spans="1:5">
+    <row r="30" ht="14.35" spans="1:5">
       <c r="A30" s="30" t="s">
         <v>195</v>
       </c>
@@ -4613,7 +4610,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="31" ht="17" spans="1:5">
+    <row r="31" ht="14.35" spans="1:5">
       <c r="A31" s="30" t="s">
         <v>108</v>
       </c>
@@ -4627,7 +4624,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="32" ht="17" spans="1:5">
+    <row r="32" ht="14.35" spans="1:5">
       <c r="A32" s="30" t="s">
         <v>54</v>
       </c>
@@ -4641,7 +4638,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" ht="17" spans="1:5">
+    <row r="33" ht="14.35" spans="1:5">
       <c r="A33" s="30" t="s">
         <v>198</v>
       </c>
@@ -4655,7 +4652,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" ht="17" spans="1:5">
+    <row r="34" ht="14.35" spans="1:5">
       <c r="A34" s="30" t="s">
         <v>200</v>
       </c>
@@ -4669,7 +4666,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" ht="17" spans="1:5">
+    <row r="35" ht="14.35" spans="1:5">
       <c r="A35" s="30" t="s">
         <v>60</v>
       </c>
@@ -4686,7 +4683,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" ht="17" spans="1:5">
+    <row r="36" ht="14.35" spans="1:5">
       <c r="A36" s="30" t="s">
         <v>88</v>
       </c>
@@ -4700,7 +4697,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="37" ht="17" spans="1:5">
+    <row r="37" ht="14.35" spans="1:5">
       <c r="A37" s="30" t="s">
         <v>57</v>
       </c>
@@ -4714,7 +4711,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" ht="17" spans="1:5">
+    <row r="38" ht="14.35" spans="1:5">
       <c r="A38" s="30" t="s">
         <v>202</v>
       </c>
@@ -4728,7 +4725,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" ht="17" spans="1:5">
+    <row r="39" ht="14.35" spans="1:5">
       <c r="A39" s="30" t="s">
         <v>204</v>
       </c>
@@ -4742,7 +4739,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" ht="17" spans="1:5">
+    <row r="40" ht="14.35" spans="1:5">
       <c r="A40" s="30" t="s">
         <v>64</v>
       </c>
@@ -4759,7 +4756,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" ht="17" spans="1:5">
+    <row r="41" ht="14.35" spans="1:5">
       <c r="A41" s="30" t="s">
         <v>4</v>
       </c>
@@ -4773,7 +4770,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="42" ht="17" spans="1:5">
+    <row r="42" ht="14.35" spans="1:5">
       <c r="A42" s="30" t="s">
         <v>124</v>
       </c>
@@ -4787,7 +4784,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" ht="17" spans="1:5">
+    <row r="43" ht="14.35" spans="1:5">
       <c r="A43" s="30" t="s">
         <v>70</v>
       </c>
@@ -4801,7 +4798,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" ht="34" spans="1:5">
+    <row r="44" ht="28.65" spans="1:5">
       <c r="A44" s="30" t="s">
         <v>208</v>
       </c>
@@ -4815,7 +4812,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="45" ht="34" spans="1:5">
+    <row r="45" ht="28.65" spans="1:5">
       <c r="A45" s="30" t="s">
         <v>212</v>
       </c>
@@ -4829,7 +4826,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" ht="34" spans="1:5">
+    <row r="46" ht="28.65" spans="1:5">
       <c r="A46" s="30" t="s">
         <v>215</v>
       </c>
@@ -4846,7 +4843,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" ht="34" spans="1:5">
+    <row r="47" ht="28.65" spans="1:5">
       <c r="A47" s="30" t="s">
         <v>220</v>
       </c>
@@ -4863,12 +4860,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" ht="20.4" spans="1:5">
+    <row r="49" ht="17.65" spans="1:5">
       <c r="A49" s="33" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="50" ht="17" spans="1:5">
+    <row r="50" ht="14.35" spans="1:5">
       <c r="A50" s="7" t="s">
         <v>50</v>
       </c>
@@ -4882,7 +4879,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="51" ht="17" spans="1:5">
+    <row r="51" ht="14.35" spans="1:5">
       <c r="A51" s="7" t="s">
         <v>6</v>
       </c>
@@ -4896,7 +4893,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" ht="17" spans="1:5">
+    <row r="52" ht="14.35" spans="1:5">
       <c r="A52" s="7" t="s">
         <v>23</v>
       </c>
@@ -4910,7 +4907,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" ht="17" spans="1:5">
+    <row r="53" ht="14.35" spans="1:5">
       <c r="A53" s="7" t="s">
         <v>72</v>
       </c>
@@ -4923,25 +4920,25 @@
       <c r="D53" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E53" s="66" t="s">
+      <c r="E53" s="53" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="72" t="s">
+      <c r="A54" s="71" t="s">
         <v>102</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="72" t="s">
+      <c r="A55" s="71" t="s">
         <v>125</v>
       </c>
       <c r="B55" s="21"/>
       <c r="C55" s="22"/>
     </row>
-    <row r="56" ht="17" spans="1:5">
+    <row r="56" ht="14.35" spans="1:5">
       <c r="A56" s="7" t="s">
         <v>75</v>
       </c>
@@ -4958,7 +4955,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" ht="17" spans="1:5">
+    <row r="57" ht="14.35" spans="1:5">
       <c r="A57" s="7" t="s">
         <v>29</v>
       </c>
@@ -4972,7 +4969,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" ht="17" spans="1:5">
+    <row r="58" ht="14.35" spans="1:5">
       <c r="A58" s="9" t="s">
         <v>34</v>
       </c>
@@ -4989,7 +4986,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" ht="17" spans="1:5">
+    <row r="59" ht="14.35" spans="1:5">
       <c r="A59" s="7" t="s">
         <v>185</v>
       </c>
@@ -5006,7 +5003,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="60" ht="17" spans="1:5">
+    <row r="60" ht="14.35" spans="1:5">
       <c r="A60" s="7" t="s">
         <v>188</v>
       </c>
@@ -5023,7 +5020,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" ht="17" spans="1:5">
+    <row r="61" ht="14.35" spans="1:5">
       <c r="A61" s="7" t="s">
         <v>180</v>
       </c>
@@ -5037,7 +5034,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" ht="17" spans="1:5">
+    <row r="62" ht="14.35" spans="1:5">
       <c r="A62" s="7" t="s">
         <v>189</v>
       </c>
@@ -5051,7 +5048,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" ht="17" spans="1:5">
+    <row r="63" ht="14.35" spans="1:5">
       <c r="A63" s="7" t="s">
         <v>43</v>
       </c>
@@ -5065,7 +5062,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="64" ht="17" spans="1:5">
+    <row r="64" ht="14.35" spans="1:5">
       <c r="A64" s="7" t="s">
         <v>192</v>
       </c>
@@ -5079,7 +5076,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" ht="17" spans="1:5">
+    <row r="65" ht="14.35" spans="1:5">
       <c r="A65" s="7" t="s">
         <v>195</v>
       </c>
@@ -5093,7 +5090,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" ht="17" spans="1:5">
+    <row r="66" ht="14.35" spans="1:5">
       <c r="A66" s="7" t="s">
         <v>88</v>
       </c>
@@ -5107,7 +5104,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="67" ht="17" spans="1:5">
+    <row r="67" ht="14.35" spans="1:5">
       <c r="A67" s="7" t="s">
         <v>108</v>
       </c>
@@ -5121,7 +5118,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" ht="17" spans="1:5">
+    <row r="68" ht="14.35" spans="1:5">
       <c r="A68" s="7" t="s">
         <v>57</v>
       </c>
@@ -5135,7 +5132,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" ht="17" spans="1:5">
+    <row r="69" ht="14.35" spans="1:5">
       <c r="A69" s="7" t="s">
         <v>54</v>
       </c>
@@ -5149,7 +5146,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="70" ht="17" spans="1:5">
+    <row r="70" ht="14.35" spans="1:5">
       <c r="A70" s="7" t="s">
         <v>202</v>
       </c>
@@ -5163,7 +5160,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="71" ht="17" spans="1:5">
+    <row r="71" ht="14.35" spans="1:5">
       <c r="A71" s="7" t="s">
         <v>198</v>
       </c>
@@ -5177,7 +5174,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="72" ht="17" spans="1:5">
+    <row r="72" ht="14.35" spans="1:5">
       <c r="A72" s="7" t="s">
         <v>204</v>
       </c>
@@ -5191,7 +5188,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="73" ht="17" spans="1:5">
+    <row r="73" ht="14.35" spans="1:5">
       <c r="A73" s="7" t="s">
         <v>200</v>
       </c>
@@ -5205,7 +5202,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="74" ht="17" spans="1:5">
+    <row r="74" ht="14.35" spans="1:5">
       <c r="A74" s="7" t="s">
         <v>64</v>
       </c>
@@ -5222,7 +5219,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" ht="17" spans="1:5">
+    <row r="75" ht="14.35" spans="1:5">
       <c r="A75" s="7" t="s">
         <v>60</v>
       </c>
@@ -5239,7 +5236,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" ht="17" spans="1:5">
+    <row r="76" ht="14.35" spans="1:5">
       <c r="A76" s="7" t="s">
         <v>26</v>
       </c>
@@ -5252,11 +5249,11 @@
       <c r="D76" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E76" s="66" t="s">
+      <c r="E76" s="53" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="77" ht="17" spans="1:5">
+    <row r="77" ht="14.35" spans="1:5">
       <c r="A77" s="7" t="s">
         <v>70</v>
       </c>
@@ -5270,7 +5267,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="78" ht="17" spans="1:5">
+    <row r="78" ht="14.35" spans="1:5">
       <c r="A78" s="7" t="s">
         <v>124</v>
       </c>
@@ -5284,7 +5281,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="79" ht="17" spans="1:5">
+    <row r="79" ht="14.35" spans="1:5">
       <c r="A79" s="7" t="s">
         <v>4</v>
       </c>
@@ -5301,12 +5298,12 @@
     <row r="80" spans="1:5">
       <c r="A80" s="7"/>
     </row>
-    <row r="81" ht="20.4" spans="1:5">
+    <row r="81" ht="17.65" spans="1:5">
       <c r="A81" s="33" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="82" ht="17" spans="1:5">
+    <row r="82" ht="14.35" spans="1:5">
       <c r="A82" s="6" t="s">
         <v>23</v>
       </c>
@@ -5325,7 +5322,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" ht="17" spans="1:5">
+    <row r="84" ht="14.35" spans="1:5">
       <c r="A84" s="30" t="s">
         <v>16</v>
       </c>
@@ -5335,11 +5332,11 @@
       <c r="C84" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D84" s="69" t="s">
+      <c r="D84" s="68" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="85" ht="17" spans="1:5">
+    <row r="85" ht="14.35" spans="1:5">
       <c r="A85" s="30" t="s">
         <v>31</v>
       </c>
@@ -5349,11 +5346,11 @@
       <c r="C85" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="D85" s="69" t="s">
+      <c r="D85" s="68" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="86" ht="17" spans="1:5">
+    <row r="86" ht="14.35" spans="1:5">
       <c r="A86" s="30" t="s">
         <v>152</v>
       </c>
@@ -5367,7 +5364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" ht="17" spans="1:5">
+    <row r="87" ht="14.35" spans="1:5">
       <c r="A87" s="30" t="s">
         <v>155</v>
       </c>
@@ -5381,7 +5378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" ht="17" spans="1:5">
+    <row r="88" ht="14.35" spans="1:5">
       <c r="A88" s="30" t="s">
         <v>158</v>
       </c>
@@ -5395,7 +5392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" ht="17" spans="1:5">
+    <row r="89" ht="14.35" spans="1:5">
       <c r="A89" s="30" t="s">
         <v>161</v>
       </c>
@@ -5409,7 +5406,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" ht="17" spans="1:5">
+    <row r="90" ht="14.35" spans="1:5">
       <c r="A90" s="30" t="s">
         <v>164</v>
       </c>
@@ -5423,7 +5420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" ht="17" spans="1:5">
+    <row r="91" ht="14.35" spans="1:5">
       <c r="A91" s="30" t="s">
         <v>167</v>
       </c>
@@ -5437,7 +5434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" ht="17" spans="1:5">
+    <row r="92" ht="14.35" spans="1:5">
       <c r="A92" s="30" t="s">
         <v>169</v>
       </c>
@@ -5451,7 +5448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" ht="17" spans="1:5">
+    <row r="93" ht="14.35" spans="1:5">
       <c r="A93" s="30" t="s">
         <v>149</v>
       </c>
@@ -5476,7 +5473,7 @@
       <c r="C94" s="9"/>
       <c r="D94" s="29"/>
     </row>
-    <row r="95" ht="17" spans="1:5">
+    <row r="95" ht="14.35" spans="1:5">
       <c r="A95" s="30" t="s">
         <v>124</v>
       </c>
@@ -5490,7 +5487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" ht="17" spans="1:5">
+    <row r="96" ht="14.35" spans="1:5">
       <c r="A96" s="30" t="s">
         <v>70</v>
       </c>
@@ -5519,18 +5516,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" customWidth="1"/>
-    <col min="7" max="7" width="29.2019230769231" customWidth="1"/>
-    <col min="9" max="9" width="29.2019230769231" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
+    <col min="7" max="7" width="29.2035398230088" customWidth="1"/>
+    <col min="9" max="9" width="29.2035398230088" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:7">
+    <row r="1" ht="20.65" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5547,7 +5544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:7">
+    <row r="2" ht="17.65" spans="1:7">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
@@ -5560,7 +5557,7 @@
       </c>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" ht="17" spans="1:7">
+    <row r="3" ht="14.35" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -5598,7 +5595,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:7">
+    <row r="5" ht="14.35" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>72</v>
       </c>
@@ -5619,7 +5616,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" ht="51" spans="1:7">
+    <row r="6" ht="43" spans="1:7">
       <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
@@ -5636,7 +5633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="34" spans="1:7">
+    <row r="7" ht="28.65" spans="1:7">
       <c r="A7" s="18" t="s">
         <v>14</v>
       </c>
@@ -5653,7 +5650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:7">
+    <row r="8" ht="14.35" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -5670,7 +5667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:7">
+    <row r="9" ht="14.35" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -5685,7 +5682,7 @@
       </c>
       <c r="E9" s="41"/>
     </row>
-    <row r="10" ht="17" spans="1:7">
+    <row r="10" ht="14.35" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -5700,7 +5697,7 @@
       </c>
       <c r="E10" s="41"/>
     </row>
-    <row r="11" ht="17" spans="1:7">
+    <row r="11" ht="14.35" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -5715,7 +5712,7 @@
       </c>
       <c r="E11" s="41"/>
     </row>
-    <row r="12" ht="17" spans="1:7">
+    <row r="12" ht="14.35" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -5730,7 +5727,7 @@
       </c>
       <c r="E12" s="34"/>
     </row>
-    <row r="13" ht="17" spans="1:7">
+    <row r="13" ht="14.35" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -5751,7 +5748,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="34"/>
     </row>
-    <row r="15" ht="20.4" spans="1:7">
+    <row r="15" ht="17.65" spans="1:7">
       <c r="A15" s="33" t="s">
         <v>45</v>
       </c>
@@ -5760,7 +5757,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="34"/>
     </row>
-    <row r="16" ht="17" spans="1:7">
+    <row r="16" ht="14.35" spans="1:7">
       <c r="A16" s="30" t="s">
         <v>46</v>
       </c>
@@ -5777,7 +5774,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="46"/>
     </row>
-    <row r="17" ht="17" spans="1:7">
+    <row r="17" ht="14.35" spans="1:7">
       <c r="A17" s="30" t="s">
         <v>23</v>
       </c>
@@ -5794,7 +5791,7 @@
       <c r="F17" s="22"/>
       <c r="G17" s="47"/>
     </row>
-    <row r="18" ht="17" spans="1:7">
+    <row r="18" ht="14.35" spans="1:7">
       <c r="A18" s="30" t="s">
         <v>6</v>
       </c>
@@ -5811,7 +5808,7 @@
       <c r="F18" s="22"/>
       <c r="G18" s="47"/>
     </row>
-    <row r="19" ht="17" spans="1:7">
+    <row r="19" ht="14.35" spans="1:7">
       <c r="A19" s="30" t="s">
         <v>26</v>
       </c>
@@ -5830,7 +5827,7 @@
       <c r="F19" s="22"/>
       <c r="G19" s="47"/>
     </row>
-    <row r="20" ht="17" spans="1:7">
+    <row r="20" ht="14.35" spans="1:7">
       <c r="A20" s="30" t="s">
         <v>50</v>
       </c>
@@ -5847,7 +5844,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="47"/>
     </row>
-    <row r="21" ht="17" spans="1:7">
+    <row r="21" ht="14.35" spans="1:7">
       <c r="A21" s="30" t="s">
         <v>75</v>
       </c>
@@ -5866,7 +5863,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="47"/>
     </row>
-    <row r="22" ht="17" spans="1:7">
+    <row r="22" ht="14.35" spans="1:7">
       <c r="A22" s="30" t="s">
         <v>72</v>
       </c>
@@ -5885,7 +5882,7 @@
       <c r="F22" s="22"/>
       <c r="G22" s="47"/>
     </row>
-    <row r="23" ht="17" spans="1:7">
+    <row r="23" ht="14.35" spans="1:7">
       <c r="A23" s="30" t="s">
         <v>29</v>
       </c>
@@ -5902,7 +5899,7 @@
       <c r="F23" s="22"/>
       <c r="G23" s="47"/>
     </row>
-    <row r="24" ht="17" spans="1:7">
+    <row r="24" ht="14.35" spans="1:7">
       <c r="A24" s="30" t="s">
         <v>182</v>
       </c>
@@ -5921,7 +5918,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="47"/>
     </row>
-    <row r="25" ht="17" spans="1:7">
+    <row r="25" ht="14.35" spans="1:7">
       <c r="A25" s="30" t="s">
         <v>185</v>
       </c>
@@ -5940,7 +5937,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="47"/>
     </row>
-    <row r="26" ht="17" spans="1:7">
+    <row r="26" ht="14.35" spans="1:7">
       <c r="A26" s="30" t="s">
         <v>81</v>
       </c>
@@ -5959,7 +5956,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="47"/>
     </row>
-    <row r="27" ht="17" spans="1:7">
+    <row r="27" ht="14.35" spans="1:7">
       <c r="A27" s="30" t="s">
         <v>37</v>
       </c>
@@ -5976,7 +5973,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="47"/>
     </row>
-    <row r="28" ht="17" spans="1:7">
+    <row r="28" ht="14.35" spans="1:7">
       <c r="A28" s="30" t="s">
         <v>129</v>
       </c>
@@ -5993,7 +5990,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="47"/>
     </row>
-    <row r="29" ht="17" spans="1:7">
+    <row r="29" ht="14.35" spans="1:7">
       <c r="A29" s="30" t="s">
         <v>84</v>
       </c>
@@ -6012,7 +6009,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="47"/>
     </row>
-    <row r="30" ht="17" spans="1:7">
+    <row r="30" ht="14.35" spans="1:7">
       <c r="A30" s="30" t="s">
         <v>40</v>
       </c>
@@ -6029,7 +6026,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="47"/>
     </row>
-    <row r="31" ht="17" spans="1:7">
+    <row r="31" ht="14.35" spans="1:7">
       <c r="A31" s="30" t="s">
         <v>132</v>
       </c>
@@ -6046,7 +6043,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="47"/>
     </row>
-    <row r="32" ht="17" spans="1:7">
+    <row r="32" ht="14.35" spans="1:7">
       <c r="A32" s="30" t="s">
         <v>43</v>
       </c>
@@ -6063,7 +6060,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="47"/>
     </row>
-    <row r="33" ht="17" spans="1:7">
+    <row r="33" ht="14.35" spans="1:7">
       <c r="A33" s="30" t="s">
         <v>192</v>
       </c>
@@ -6080,7 +6077,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="47"/>
     </row>
-    <row r="34" ht="17" spans="1:7">
+    <row r="34" ht="14.35" spans="1:7">
       <c r="A34" s="30" t="s">
         <v>228</v>
       </c>
@@ -6097,7 +6094,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="47"/>
     </row>
-    <row r="35" ht="17" spans="1:7">
+    <row r="35" ht="14.35" spans="1:7">
       <c r="A35" s="30" t="s">
         <v>230</v>
       </c>
@@ -6114,7 +6111,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="47"/>
     </row>
-    <row r="36" ht="17" spans="1:7">
+    <row r="36" ht="14.35" spans="1:7">
       <c r="A36" s="30" t="s">
         <v>233</v>
       </c>
@@ -6131,7 +6128,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="50"/>
     </row>
-    <row r="37" ht="17" spans="1:7">
+    <row r="37" ht="14.35" spans="1:7">
       <c r="A37" s="30" t="s">
         <v>234</v>
       </c>
@@ -6148,7 +6145,7 @@
       <c r="F37" s="22"/>
       <c r="G37" s="47"/>
     </row>
-    <row r="38" ht="17" spans="1:7">
+    <row r="38" ht="14.35" spans="1:7">
       <c r="A38" s="30" t="s">
         <v>235</v>
       </c>
@@ -6165,7 +6162,7 @@
       <c r="F38" s="22"/>
       <c r="G38" s="47"/>
     </row>
-    <row r="39" ht="17" spans="1:7">
+    <row r="39" ht="14.35" spans="1:7">
       <c r="A39" s="30" t="s">
         <v>236</v>
       </c>
@@ -6182,7 +6179,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="47"/>
     </row>
-    <row r="40" ht="17" spans="1:7">
+    <row r="40" ht="14.35" spans="1:7">
       <c r="A40" s="30" t="s">
         <v>237</v>
       </c>
@@ -6201,7 +6198,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="47"/>
     </row>
-    <row r="41" ht="17" spans="1:7">
+    <row r="41" ht="14.35" spans="1:7">
       <c r="A41" s="30" t="s">
         <v>238</v>
       </c>
@@ -6218,7 +6215,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="50"/>
     </row>
-    <row r="42" ht="17" spans="1:7">
+    <row r="42" ht="14.35" spans="1:7">
       <c r="A42" s="30" t="s">
         <v>239</v>
       </c>
@@ -6235,7 +6232,7 @@
       <c r="F42" s="22"/>
       <c r="G42" s="47"/>
     </row>
-    <row r="43" ht="17" spans="1:7">
+    <row r="43" ht="14.35" spans="1:7">
       <c r="A43" s="30" t="s">
         <v>240</v>
       </c>
@@ -6252,7 +6249,7 @@
       <c r="F43" s="22"/>
       <c r="G43" s="47"/>
     </row>
-    <row r="44" ht="17" spans="1:7">
+    <row r="44" ht="14.35" spans="1:7">
       <c r="A44" s="30" t="s">
         <v>241</v>
       </c>
@@ -6269,7 +6266,7 @@
       <c r="F44" s="9"/>
       <c r="G44" s="47"/>
     </row>
-    <row r="45" ht="17" spans="1:7">
+    <row r="45" ht="14.35" spans="1:7">
       <c r="A45" s="30" t="s">
         <v>242</v>
       </c>
@@ -6288,7 +6285,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="47"/>
     </row>
-    <row r="46" ht="17" spans="1:7">
+    <row r="46" ht="14.35" spans="1:7">
       <c r="A46" s="30" t="s">
         <v>4</v>
       </c>
@@ -6305,7 +6302,7 @@
       <c r="F46" s="52"/>
       <c r="G46" s="47"/>
     </row>
-    <row r="47" ht="17" spans="1:7">
+    <row r="47" ht="14.35" spans="1:7">
       <c r="A47" s="30" t="s">
         <v>124</v>
       </c>
@@ -6322,7 +6319,7 @@
       <c r="F47" s="52"/>
       <c r="G47" s="47"/>
     </row>
-    <row r="48" ht="17" spans="1:7">
+    <row r="48" ht="14.35" spans="1:7">
       <c r="A48" s="30" t="s">
         <v>70</v>
       </c>
@@ -6339,7 +6336,7 @@
       <c r="F48" s="52"/>
       <c r="G48" s="47"/>
     </row>
-    <row r="49" ht="34" spans="1:7">
+    <row r="49" ht="28.65" spans="1:7">
       <c r="A49" s="30" t="s">
         <v>208</v>
       </c>
@@ -6356,7 +6353,7 @@
       <c r="F49" s="52"/>
       <c r="G49" s="47"/>
     </row>
-    <row r="50" ht="34" spans="1:7">
+    <row r="50" ht="28.65" spans="1:7">
       <c r="A50" s="30" t="s">
         <v>212</v>
       </c>
@@ -6371,7 +6368,7 @@
       </c>
       <c r="E50" s="41"/>
     </row>
-    <row r="51" ht="34" spans="1:7">
+    <row r="51" ht="28.65" spans="1:7">
       <c r="A51" s="30" t="s">
         <v>215</v>
       </c>
@@ -6388,7 +6385,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="52" ht="34" spans="1:7">
+    <row r="52" ht="28.65" spans="1:7">
       <c r="A52" s="30" t="s">
         <v>220</v>
       </c>
@@ -6411,7 +6408,7 @@
       <c r="D53" s="10"/>
       <c r="E53" s="34"/>
     </row>
-    <row r="54" ht="20.4" spans="1:7">
+    <row r="54" ht="17.65" spans="1:7">
       <c r="A54" s="33" t="s">
         <v>224</v>
       </c>
@@ -6420,7 +6417,7 @@
       <c r="D54" s="10"/>
       <c r="E54" s="34"/>
     </row>
-    <row r="55" ht="17" spans="1:7">
+    <row r="55" ht="14.35" spans="1:7">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -6435,7 +6432,7 @@
       </c>
       <c r="E55" s="41"/>
     </row>
-    <row r="56" ht="17" spans="1:7">
+    <row r="56" ht="14.35" spans="1:7">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -6450,7 +6447,7 @@
       </c>
       <c r="E56" s="41"/>
     </row>
-    <row r="57" ht="17" spans="1:7">
+    <row r="57" ht="14.35" spans="1:7">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -6465,7 +6462,7 @@
       </c>
       <c r="E57" s="41"/>
     </row>
-    <row r="58" ht="17" spans="1:7">
+    <row r="58" ht="14.35" spans="1:7">
       <c r="A58" s="1" t="s">
         <v>72</v>
       </c>
@@ -6500,7 +6497,7 @@
       <c r="D60" s="54"/>
       <c r="E60" s="41"/>
     </row>
-    <row r="61" ht="17" spans="1:7">
+    <row r="61" ht="14.35" spans="1:7">
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
@@ -6517,7 +6514,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" ht="17" spans="1:7">
+    <row r="62" ht="14.35" spans="1:7">
       <c r="A62" s="1" t="s">
         <v>29</v>
       </c>
@@ -6532,7 +6529,7 @@
       </c>
       <c r="E62" s="56"/>
     </row>
-    <row r="63" ht="17" spans="1:7">
+    <row r="63" ht="14.35" spans="1:7">
       <c r="A63" s="18" t="s">
         <v>34</v>
       </c>
@@ -6549,7 +6546,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" ht="17" spans="1:7">
+    <row r="64" ht="14.35" spans="1:7">
       <c r="A64" s="1" t="s">
         <v>48</v>
       </c>
@@ -6566,7 +6563,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="65" ht="17" spans="1:5">
+    <row r="65" ht="14.35" spans="1:5">
       <c r="A65" s="1" t="s">
         <v>185</v>
       </c>
@@ -6583,7 +6580,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="66" ht="17" spans="1:5">
+    <row r="66" ht="14.35" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>81</v>
       </c>
@@ -6600,7 +6597,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" ht="17" spans="1:5">
+    <row r="67" ht="14.35" spans="1:5">
       <c r="A67" s="1" t="s">
         <v>37</v>
       </c>
@@ -6615,7 +6612,7 @@
       </c>
       <c r="E67" s="56"/>
     </row>
-    <row r="68" ht="17" spans="1:5">
+    <row r="68" ht="14.35" spans="1:5">
       <c r="A68" s="1" t="s">
         <v>129</v>
       </c>
@@ -6630,7 +6627,7 @@
       </c>
       <c r="E68" s="56"/>
     </row>
-    <row r="69" ht="17" spans="1:5">
+    <row r="69" ht="14.35" spans="1:5">
       <c r="A69" s="1" t="s">
         <v>84</v>
       </c>
@@ -6647,7 +6644,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" ht="17" spans="1:5">
+    <row r="70" ht="14.35" spans="1:5">
       <c r="A70" s="1" t="s">
         <v>40</v>
       </c>
@@ -6662,7 +6659,7 @@
       </c>
       <c r="E70" s="56"/>
     </row>
-    <row r="71" ht="17" spans="1:5">
+    <row r="71" ht="14.35" spans="1:5">
       <c r="A71" s="1" t="s">
         <v>132</v>
       </c>
@@ -6677,7 +6674,7 @@
       </c>
       <c r="E71" s="56"/>
     </row>
-    <row r="72" ht="17" spans="1:5">
+    <row r="72" ht="14.35" spans="1:5">
       <c r="A72" s="1" t="s">
         <v>43</v>
       </c>
@@ -6692,7 +6689,7 @@
       </c>
       <c r="E72" s="56"/>
     </row>
-    <row r="73" ht="17" spans="1:5">
+    <row r="73" ht="14.35" spans="1:5">
       <c r="A73" s="1" t="s">
         <v>192</v>
       </c>
@@ -6707,7 +6704,7 @@
       </c>
       <c r="E73" s="56"/>
     </row>
-    <row r="74" ht="17" spans="1:5">
+    <row r="74" ht="14.35" spans="1:5">
       <c r="A74" s="1" t="s">
         <v>228</v>
       </c>
@@ -6722,7 +6719,7 @@
       </c>
       <c r="E74" s="56"/>
     </row>
-    <row r="75" ht="17" spans="1:5">
+    <row r="75" ht="14.35" spans="1:5">
       <c r="A75" s="1" t="s">
         <v>230</v>
       </c>
@@ -6737,7 +6734,7 @@
       </c>
       <c r="E75" s="56"/>
     </row>
-    <row r="76" ht="17" spans="1:5">
+    <row r="76" ht="14.35" spans="1:5">
       <c r="A76" s="1" t="s">
         <v>238</v>
       </c>
@@ -6752,7 +6749,7 @@
       </c>
       <c r="E76" s="56"/>
     </row>
-    <row r="77" ht="17" spans="1:5">
+    <row r="77" ht="14.35" spans="1:5">
       <c r="A77" s="1" t="s">
         <v>233</v>
       </c>
@@ -6767,7 +6764,7 @@
       </c>
       <c r="E77" s="56"/>
     </row>
-    <row r="78" ht="17" spans="1:5">
+    <row r="78" ht="14.35" spans="1:5">
       <c r="A78" s="1" t="s">
         <v>239</v>
       </c>
@@ -6782,7 +6779,7 @@
       </c>
       <c r="E78" s="56"/>
     </row>
-    <row r="79" ht="17" spans="1:5">
+    <row r="79" ht="14.35" spans="1:5">
       <c r="A79" s="1" t="s">
         <v>234</v>
       </c>
@@ -6797,7 +6794,7 @@
       </c>
       <c r="E79" s="56"/>
     </row>
-    <row r="80" ht="17" spans="1:5">
+    <row r="80" ht="14.35" spans="1:5">
       <c r="A80" s="1" t="s">
         <v>240</v>
       </c>
@@ -6812,7 +6809,7 @@
       </c>
       <c r="E80" s="56"/>
     </row>
-    <row r="81" ht="17" spans="1:5">
+    <row r="81" ht="14.35" spans="1:5">
       <c r="A81" s="1" t="s">
         <v>235</v>
       </c>
@@ -6827,7 +6824,7 @@
       </c>
       <c r="E81" s="56"/>
     </row>
-    <row r="82" ht="17" spans="1:5">
+    <row r="82" ht="14.35" spans="1:5">
       <c r="A82" s="1" t="s">
         <v>241</v>
       </c>
@@ -6842,7 +6839,7 @@
       </c>
       <c r="E82" s="56"/>
     </row>
-    <row r="83" ht="17" spans="1:5">
+    <row r="83" ht="14.35" spans="1:5">
       <c r="A83" s="1" t="s">
         <v>236</v>
       </c>
@@ -6857,7 +6854,7 @@
       </c>
       <c r="E83" s="56"/>
     </row>
-    <row r="84" ht="17" spans="1:5">
+    <row r="84" ht="14.35" spans="1:5">
       <c r="A84" s="1" t="s">
         <v>242</v>
       </c>
@@ -6874,7 +6871,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" ht="17" spans="1:5">
+    <row r="85" ht="14.35" spans="1:5">
       <c r="A85" s="1" t="s">
         <v>237</v>
       </c>
@@ -6891,7 +6888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" ht="17" spans="1:5">
+    <row r="86" ht="14.35" spans="1:5">
       <c r="A86" s="1" t="s">
         <v>26</v>
       </c>
@@ -6908,7 +6905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" ht="17" spans="1:5">
+    <row r="87" ht="14.35" spans="1:5">
       <c r="A87" s="1" t="s">
         <v>70</v>
       </c>
@@ -6923,7 +6920,7 @@
       </c>
       <c r="E87" s="34"/>
     </row>
-    <row r="88" ht="17" spans="1:5">
+    <row r="88" ht="14.35" spans="1:5">
       <c r="A88" s="1" t="s">
         <v>124</v>
       </c>
@@ -6938,7 +6935,7 @@
       </c>
       <c r="E88" s="34"/>
     </row>
-    <row r="89" ht="17" spans="1:5">
+    <row r="89" ht="14.35" spans="1:5">
       <c r="A89" s="1" t="s">
         <v>4</v>
       </c>
@@ -6953,12 +6950,12 @@
       </c>
       <c r="E89" s="34"/>
     </row>
-    <row r="91" ht="20.4" spans="1:5">
+    <row r="91" ht="17.65" spans="1:5">
       <c r="A91" s="33" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="92" ht="17" spans="1:5">
+    <row r="92" ht="14.35" spans="1:5">
       <c r="A92" s="45" t="s">
         <v>23</v>
       </c>
@@ -6977,7 +6974,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="94" ht="17" spans="1:5">
+    <row r="94" ht="14.35" spans="1:5">
       <c r="A94" s="6" t="s">
         <v>16</v>
       </c>
@@ -6991,7 +6988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" ht="17" spans="1:5">
+    <row r="95" ht="14.35" spans="1:5">
       <c r="A95" s="6" t="s">
         <v>31</v>
       </c>
@@ -7005,7 +7002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" ht="17" spans="1:5">
+    <row r="96" ht="14.35" spans="1:5">
       <c r="A96" s="6" t="s">
         <v>152</v>
       </c>
@@ -7019,7 +7016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" ht="17" spans="1:5">
+    <row r="97" ht="14.35" spans="1:5">
       <c r="A97" s="6" t="s">
         <v>155</v>
       </c>
@@ -7033,7 +7030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" ht="17" spans="1:5">
+    <row r="98" ht="14.35" spans="1:5">
       <c r="A98" s="6" t="s">
         <v>158</v>
       </c>
@@ -7047,7 +7044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" ht="17" spans="1:5">
+    <row r="99" ht="14.35" spans="1:5">
       <c r="A99" s="6" t="s">
         <v>161</v>
       </c>
@@ -7061,7 +7058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" ht="17" spans="1:5">
+    <row r="100" ht="14.35" spans="1:5">
       <c r="A100" s="6" t="s">
         <v>164</v>
       </c>
@@ -7075,7 +7072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" ht="17" spans="1:5">
+    <row r="101" ht="14.35" spans="1:5">
       <c r="A101" s="6" t="s">
         <v>167</v>
       </c>
@@ -7089,7 +7086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" ht="17" spans="1:5">
+    <row r="102" ht="14.35" spans="1:5">
       <c r="A102" s="6" t="s">
         <v>169</v>
       </c>
@@ -7103,7 +7100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" ht="17" spans="1:5">
+    <row r="103" ht="14.35" spans="1:5">
       <c r="A103" s="6" t="s">
         <v>149</v>
       </c>
@@ -7128,7 +7125,7 @@
       <c r="C104" s="7"/>
       <c r="D104" s="29"/>
     </row>
-    <row r="105" ht="17" spans="1:5">
+    <row r="105" ht="14.35" spans="1:5">
       <c r="A105" s="6" t="s">
         <v>124</v>
       </c>
@@ -7142,7 +7139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" ht="17" spans="1:5">
+    <row r="106" ht="14.35" spans="1:5">
       <c r="A106" s="6" t="s">
         <v>70</v>
       </c>
@@ -7235,16 +7232,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:5">
+    <row r="1" ht="20.65" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7261,14 +7258,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:5">
+    <row r="2" ht="17.65" spans="1:5">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
     </row>
-    <row r="3" ht="17" spans="1:5">
+    <row r="3" ht="14.35" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>245</v>
       </c>
@@ -7282,7 +7279,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" ht="16.8" customHeight="1" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>152</v>
       </c>
@@ -7374,7 +7371,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" ht="20.4" spans="1:5">
+    <row r="11" ht="17.65" spans="1:5">
       <c r="A11" s="33" t="s">
         <v>45</v>
       </c>
@@ -7382,7 +7379,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" ht="17" spans="1:5">
+    <row r="12" ht="14.35" spans="1:5">
       <c r="A12" s="6" t="s">
         <v>247</v>
       </c>
@@ -7514,7 +7511,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="1:5">
+    <row r="21" ht="14.35" spans="1:5">
       <c r="A21" s="6" t="s">
         <v>124</v>
       </c>
@@ -7528,7 +7525,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="1:5">
+    <row r="22" ht="14.35" spans="1:5">
       <c r="A22" s="6" t="s">
         <v>70</v>
       </c>
@@ -7552,16 +7549,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:5">
+    <row r="1" ht="20.65" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7578,7 +7575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:5">
+    <row r="2" ht="17.65" spans="1:5">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -7597,7 +7594,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="4" ht="17" spans="1:5">
+    <row r="4" ht="14.35" spans="1:5">
       <c r="A4" s="22" t="s">
         <v>16</v>
       </c>
@@ -7639,7 +7636,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:5">
+    <row r="7" ht="14.35" spans="1:5">
       <c r="A7" s="22" t="s">
         <v>245</v>
       </c>
@@ -7670,7 +7667,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="10" ht="20.4" spans="1:5">
+    <row r="10" ht="17.65" spans="1:5">
       <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
@@ -7689,7 +7686,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:5">
+    <row r="12" ht="14.35" spans="1:5">
       <c r="A12" s="30" t="s">
         <v>277</v>
       </c>
@@ -7717,7 +7714,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:5">
+    <row r="14" ht="14.35" spans="1:5">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
@@ -7762,7 +7759,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:4">
+    <row r="17" ht="14.35" spans="1:4">
       <c r="A17" s="6" t="s">
         <v>280</v>
       </c>
@@ -7902,7 +7899,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" ht="34" spans="1:4">
+    <row r="27" ht="14.35" spans="1:4">
       <c r="A27" s="6" t="s">
         <v>302</v>
       </c>
@@ -7940,22 +7937,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="13" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" style="13" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" style="13" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" style="14" customWidth="1"/>
-    <col min="6" max="6" width="42.1442307692308" style="13" customWidth="1"/>
-    <col min="7" max="7" width="27.3076923076923" style="13" customWidth="1"/>
-    <col min="8" max="8" width="24.8461538461538" style="13" customWidth="1"/>
-    <col min="9" max="9" width="37.0096153846154" style="15" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="13" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" style="13" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" style="14" customWidth="1"/>
+    <col min="6" max="6" width="42.141592920354" style="13" customWidth="1"/>
+    <col min="7" max="7" width="27.3097345132743" style="13" customWidth="1"/>
+    <col min="8" max="8" width="24.8495575221239" style="13" customWidth="1"/>
+    <col min="9" max="9" width="37.0088495575221" style="15" customWidth="1"/>
     <col min="10" max="10" width="9" style="15"/>
-    <col min="11" max="11" width="29.2019230769231" style="15" customWidth="1"/>
+    <col min="11" max="11" width="29.2035398230088" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:11">
+    <row r="1" ht="20.65" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7986,7 +7983,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" ht="20.4" spans="1:11">
+    <row r="2" ht="17.65" spans="1:11">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -7995,7 +7992,7 @@
       </c>
       <c r="K2" s="17"/>
     </row>
-    <row r="3" ht="17" spans="1:11">
+    <row r="3" ht="14.35" spans="1:11">
       <c r="A3" s="18" t="s">
         <v>16</v>
       </c>
@@ -8023,7 +8020,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
+    <row r="4" ht="16.8" customHeight="1" spans="1:11">
       <c r="A4" s="18" t="s">
         <v>31</v>
       </c>
@@ -8050,7 +8047,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:11">
+    <row r="5" ht="14.35" spans="1:11">
       <c r="A5" s="18" t="s">
         <v>245</v>
       </c>
@@ -8073,7 +8070,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" ht="34" spans="1:11">
+    <row r="6" ht="28.65" spans="1:11">
       <c r="A6" s="18" t="s">
         <v>274</v>
       </c>
@@ -8194,7 +8191,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="12" ht="20.4" spans="1:11">
+    <row r="12" ht="17.65" spans="1:11">
       <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
@@ -8222,7 +8219,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:11">
+    <row r="14" ht="14.35" spans="1:11">
       <c r="A14" s="7" t="s">
         <v>245</v>
       </c>
@@ -8242,7 +8239,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:11">
+    <row r="15" ht="14.35" spans="1:11">
       <c r="A15" s="7" t="s">
         <v>334</v>
       </c>
@@ -8308,7 +8305,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" ht="34" spans="1:9">
+    <row r="18" ht="28.65" spans="1:9">
       <c r="A18" s="7" t="s">
         <v>274</v>
       </c>
@@ -8337,7 +8334,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:9">
+    <row r="19" ht="14.35" spans="1:9">
       <c r="A19" s="7" t="s">
         <v>16</v>
       </c>
@@ -8462,7 +8459,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" ht="68" spans="1:9">
+    <row r="26" ht="57.35" spans="1:9">
       <c r="A26" s="7" t="s">
         <v>290</v>
       </c>
@@ -8488,7 +8485,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" ht="51" spans="1:9">
+    <row r="27" ht="28.65" spans="1:9">
       <c r="A27" s="7" t="s">
         <v>296</v>
       </c>
@@ -8514,7 +8511,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28" ht="34" spans="1:9">
+    <row r="28" ht="28.65" spans="1:9">
       <c r="A28" s="7" t="s">
         <v>302</v>
       </c>
@@ -8551,16 +8548,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2307692307692" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.1442307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3076923076923" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8461538461538" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.0096153846154" style="2" customWidth="1"/>
+    <col min="1" max="1" width="44.2300884955752" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3097345132743" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.8495575221239" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.0088495575221" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:5">
+    <row r="1" ht="20.65" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8577,7 +8574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:5">
+    <row r="2" ht="17.65" spans="1:5">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -8596,7 +8593,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" ht="16.8" customHeight="1" spans="1:5">
       <c r="A4" s="6" t="s">
         <v>365</v>
       </c>
@@ -8610,12 +8607,12 @@
         <v>364</v>
       </c>
     </row>
-    <row r="6" ht="20.4" spans="1:5">
+    <row r="6" ht="17.65" spans="1:5">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" ht="20.4" spans="1:5">
+    <row r="7" ht="17.65" spans="1:5">
       <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>47</v>
@@ -8642,7 +8639,7 @@
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" ht="17" spans="1:5">
+    <row r="9" ht="14.35" spans="1:5">
       <c r="A9" s="6" t="s">
         <v>367</v>
       </c>
@@ -8717,7 +8714,7 @@
       </c>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" ht="17" spans="1:5">
+    <row r="14" ht="14.35" spans="1:5">
       <c r="A14" s="6" t="s">
         <v>375</v>
       </c>
@@ -8732,7 +8729,7 @@
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" ht="68" spans="1:5">
+    <row r="15" ht="57.35" spans="1:5">
       <c r="A15" s="6" t="s">
         <v>377</v>
       </c>
@@ -8743,12 +8740,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="17" ht="20.4" spans="1:5">
+    <row r="17" ht="17.65" spans="1:5">
       <c r="A17" s="12" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="18" ht="17" spans="1:5">
+    <row r="18" ht="14.35" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>380</v>
       </c>
@@ -8759,7 +8756,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:5">
+    <row r="19" ht="14.35" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>382</v>
       </c>
@@ -8784,7 +8781,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="1:5">
+    <row r="21" ht="14.35" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>385</v>
       </c>
@@ -8798,7 +8795,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22" ht="34" spans="1:5">
+    <row r="22" ht="14.35" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>386</v>
       </c>
@@ -8806,7 +8803,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="23" ht="68" spans="1:5">
+    <row r="23" ht="43" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>388</v>
       </c>
@@ -8814,7 +8811,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="24" ht="17" spans="1:5">
+    <row r="24" ht="14.35" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>390</v>
       </c>

--- a/开发设计/字段对应关系.xlsx
+++ b/开发设计/字段对应关系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18240" windowHeight="8360" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="全额交易查询" sheetId="10" r:id="rId1"/>
@@ -105,7 +105,7 @@
   </si>
   <si>
     <t>判断买方持有人账号是否是两个上清托管账号之一，如果是则取买方交易状态，否则取卖方交易状态
-枚举值：14.23.买卖方交易状态</t>
+枚举值：14.22.买卖方结算确认状态</t>
   </si>
   <si>
     <t>交易编号</t>
@@ -2308,8 +2308,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8255635" y="711200"/>
-          <a:ext cx="110490" cy="366395"/>
+          <a:off x="8761095" y="709295"/>
+          <a:ext cx="110490" cy="355600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2347,8 +2347,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8230235" y="918210"/>
-          <a:ext cx="114300" cy="150495"/>
+          <a:off x="8735695" y="916305"/>
+          <a:ext cx="114300" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2391,8 +2391,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="19816445"/>
-          <a:ext cx="114300" cy="150495"/>
+          <a:off x="0" y="18784570"/>
+          <a:ext cx="114300" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2430,8 +2430,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="19816445"/>
-          <a:ext cx="114300" cy="150495"/>
+          <a:off x="0" y="18784570"/>
+          <a:ext cx="114300" cy="139700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2469,8 +2469,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="19998690"/>
-          <a:ext cx="110490" cy="154940"/>
+          <a:off x="0" y="18956020"/>
+          <a:ext cx="110490" cy="144145"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2508,8 +2508,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="19998690"/>
-          <a:ext cx="110490" cy="154940"/>
+          <a:off x="0" y="18956020"/>
+          <a:ext cx="110490" cy="144145"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2776,16 +2776,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E94"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="72" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="72" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" customWidth="1"/>
+    <col min="4" max="4" width="24.85" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:5">
+    <row r="1" ht="20.25" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2802,12 +2802,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17.65" spans="1:5">
+    <row r="2" ht="18.75" spans="1:5">
       <c r="A2" s="73" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="14.35" spans="1:5">
+    <row r="3" spans="1:5">
       <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="E3" s="74"/>
     </row>
-    <row r="4" ht="43" spans="1:5">
+    <row r="4" ht="40.5" spans="1:5">
       <c r="A4" s="45" t="s">
         <v>10</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="28.65" spans="1:5">
+    <row r="5" ht="27" spans="1:5">
       <c r="A5" s="45" t="s">
         <v>14</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" ht="14.35" spans="1:5">
+    <row r="6" spans="1:5">
       <c r="A6" s="17" t="s">
         <v>16</v>
       </c>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E6" s="74"/>
     </row>
-    <row r="7" ht="57.35" spans="1:5">
+    <row r="7" ht="54" spans="1:5">
       <c r="A7" s="45" t="s">
         <v>19</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" ht="14.35" spans="1:5">
+    <row r="8" spans="1:5">
       <c r="A8" s="17" t="s">
         <v>23</v>
       </c>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E8" s="74"/>
     </row>
-    <row r="9" ht="14.35" spans="1:5">
+    <row r="9" spans="1:5">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="14.35" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10" s="17" t="s">
         <v>29</v>
       </c>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E10" s="74"/>
     </row>
-    <row r="11" ht="14.35" spans="1:5">
+    <row r="11" spans="1:5">
       <c r="A11" s="17" t="s">
         <v>31</v>
       </c>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="E11" s="74"/>
     </row>
-    <row r="12" ht="57.35" spans="1:5">
+    <row r="12" ht="54" spans="1:5">
       <c r="A12" s="45" t="s">
         <v>33</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" ht="14.35" spans="1:5">
+    <row r="13" spans="1:5">
       <c r="A13" s="17" t="s">
         <v>34</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="14.35" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E14" s="74"/>
     </row>
-    <row r="15" ht="14.35" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15" s="17" t="s">
         <v>40</v>
       </c>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="E15" s="74"/>
     </row>
-    <row r="16" ht="14.35" spans="1:5">
+    <row r="16" spans="1:5">
       <c r="A16" s="17" t="s">
         <v>43</v>
       </c>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E16" s="74"/>
     </row>
-    <row r="18" ht="17.65" spans="1:5">
+    <row r="18" ht="18.75" spans="1:5">
       <c r="A18" s="73" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" ht="14.35" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" s="35" t="s">
         <v>46</v>
       </c>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E19" s="40"/>
     </row>
-    <row r="20" ht="14.35" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20" s="35" t="s">
         <v>23</v>
       </c>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="E20" s="40"/>
     </row>
-    <row r="21" ht="14.35" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" s="35" t="s">
         <v>6</v>
       </c>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="E21" s="40"/>
     </row>
-    <row r="22" ht="14.35" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" s="35" t="s">
         <v>26</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" ht="14.35" spans="1:5">
+    <row r="23" spans="1:5">
       <c r="A23" s="35" t="s">
         <v>48</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" ht="14.35" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24" s="35" t="s">
         <v>50</v>
       </c>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E24" s="40"/>
     </row>
-    <row r="25" ht="14.35" spans="1:5">
+    <row r="25" spans="1:5">
       <c r="A25" s="35" t="s">
         <v>37</v>
       </c>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="E25" s="40"/>
     </row>
-    <row r="26" ht="14.35" spans="1:5">
+    <row r="26" spans="1:5">
       <c r="A26" s="35" t="s">
         <v>52</v>
       </c>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="E26" s="40"/>
     </row>
-    <row r="27" ht="14.35" spans="1:5">
+    <row r="27" spans="1:5">
       <c r="A27" s="35" t="s">
         <v>55</v>
       </c>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="E27" s="40"/>
     </row>
-    <row r="28" ht="14.35" spans="1:5">
+    <row r="28" spans="1:5">
       <c r="A28" s="35" t="s">
         <v>58</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" ht="14.35" spans="1:5">
+    <row r="29" spans="1:5">
       <c r="A29" s="35" t="s">
         <v>62</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" ht="14.35" spans="1:5">
+    <row r="30" spans="1:5">
       <c r="A30" s="84" t="s">
         <v>65</v>
       </c>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E30" s="40"/>
     </row>
-    <row r="31" ht="14.35" spans="1:5">
+    <row r="31" spans="1:5">
       <c r="A31" s="84" t="s">
         <v>68</v>
       </c>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E31" s="50"/>
     </row>
-    <row r="33" ht="17.65" spans="1:5">
+    <row r="33" ht="18.75" spans="1:5">
       <c r="A33" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="34" ht="14.35" spans="1:5">
+    <row r="34" spans="1:5">
       <c r="A34" s="84" t="s">
         <v>50</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E34" s="50"/>
     </row>
-    <row r="35" ht="14.35" spans="1:5">
+    <row r="35" spans="1:5">
       <c r="A35" s="84" t="s">
         <v>72</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" ht="14.35" spans="1:5">
+    <row r="36" spans="1:5">
       <c r="A36" s="84" t="s">
         <v>75</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" ht="14.35" spans="1:5">
+    <row r="37" spans="1:5">
       <c r="A37" s="84" t="s">
         <v>34</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" ht="14.35" spans="1:5">
+    <row r="38" spans="1:5">
       <c r="A38" s="84" t="s">
         <v>79</v>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E38" s="50"/>
     </row>
-    <row r="39" ht="14.35" spans="1:5">
+    <row r="39" spans="1:5">
       <c r="A39" s="84" t="s">
         <v>81</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" ht="14.35" spans="1:5">
+    <row r="40" spans="1:5">
       <c r="A40" s="84" t="s">
         <v>84</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" ht="14.35" spans="1:5">
+    <row r="41" spans="1:5">
       <c r="A41" s="84" t="s">
         <v>86</v>
       </c>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="E41" s="50"/>
     </row>
-    <row r="42" ht="14.35" spans="1:5">
+    <row r="42" spans="1:5">
       <c r="A42" s="84" t="s">
         <v>55</v>
       </c>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E42" s="50"/>
     </row>
-    <row r="43" ht="14.35" spans="1:5">
+    <row r="43" spans="1:5">
       <c r="A43" s="84" t="s">
         <v>89</v>
       </c>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="E43" s="50"/>
     </row>
-    <row r="44" ht="14.35" spans="1:5">
+    <row r="44" spans="1:5">
       <c r="A44" s="84" t="s">
         <v>92</v>
       </c>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E44" s="50"/>
     </row>
-    <row r="45" ht="14.35" spans="1:5">
+    <row r="45" spans="1:5">
       <c r="A45" s="84" t="s">
         <v>95</v>
       </c>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E45" s="50"/>
     </row>
-    <row r="46" ht="14.35" spans="1:5">
+    <row r="46" spans="1:5">
       <c r="A46" s="84" t="s">
         <v>62</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" ht="14.35" spans="1:5">
+    <row r="47" spans="1:5">
       <c r="A47" s="84" t="s">
         <v>98</v>
       </c>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="E47" s="50"/>
     </row>
-    <row r="48" ht="14.35" spans="1:5">
+    <row r="48" spans="1:5">
       <c r="A48" s="84" t="s">
         <v>26</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" ht="14.35" spans="1:5">
+    <row r="49" spans="1:5">
       <c r="A49" s="84" t="s">
         <v>70</v>
       </c>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="E49" s="50"/>
     </row>
-    <row r="50" ht="14.35" spans="1:5">
+    <row r="50" spans="1:5">
       <c r="A50" s="84" t="s">
         <v>4</v>
       </c>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E50" s="50"/>
     </row>
-    <row r="51" ht="14.35" spans="1:5">
+    <row r="51" spans="1:5">
       <c r="A51" s="84" t="s">
         <v>6</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="E51" s="50"/>
     </row>
-    <row r="52" ht="14.35" spans="1:5">
+    <row r="52" spans="1:5">
       <c r="A52" s="84" t="s">
         <v>102</v>
       </c>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E52" s="50"/>
     </row>
-    <row r="53" ht="14.35" spans="1:5">
+    <row r="53" spans="1:5">
       <c r="A53" s="84" t="s">
         <v>29</v>
       </c>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="E53" s="50"/>
     </row>
-    <row r="54" ht="14.35" spans="1:5">
+    <row r="54" spans="1:5">
       <c r="A54" s="84" t="s">
         <v>48</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" ht="14.35" spans="1:5">
+    <row r="55" spans="1:5">
       <c r="A55" s="84" t="s">
         <v>104</v>
       </c>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E55" s="50"/>
     </row>
-    <row r="56" ht="14.35" spans="1:5">
+    <row r="56" spans="1:5">
       <c r="A56" s="84" t="s">
         <v>37</v>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E56" s="50"/>
     </row>
-    <row r="57" ht="14.35" spans="1:5">
+    <row r="57" spans="1:5">
       <c r="A57" s="84" t="s">
         <v>40</v>
       </c>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="E57" s="50"/>
     </row>
-    <row r="58" ht="14.35" spans="1:5">
+    <row r="58" spans="1:5">
       <c r="A58" s="84" t="s">
         <v>106</v>
       </c>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E58" s="50"/>
     </row>
-    <row r="59" ht="14.35" spans="1:5">
+    <row r="59" spans="1:5">
       <c r="A59" s="84" t="s">
         <v>52</v>
       </c>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E59" s="50"/>
     </row>
-    <row r="60" ht="14.35" spans="1:5">
+    <row r="60" spans="1:5">
       <c r="A60" s="84" t="s">
         <v>109</v>
       </c>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E60" s="50"/>
     </row>
-    <row r="61" ht="14.35" spans="1:5">
+    <row r="61" spans="1:5">
       <c r="A61" s="84" t="s">
         <v>112</v>
       </c>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="E61" s="50"/>
     </row>
-    <row r="62" ht="14.35" spans="1:5">
+    <row r="62" spans="1:5">
       <c r="A62" s="84" t="s">
         <v>115</v>
       </c>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="E62" s="50"/>
     </row>
-    <row r="63" ht="14.35" spans="1:5">
+    <row r="63" spans="1:5">
       <c r="A63" s="84" t="s">
         <v>58</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" ht="14.35" spans="1:5">
+    <row r="64" spans="1:5">
       <c r="A64" s="84" t="s">
         <v>118</v>
       </c>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="E64" s="50"/>
     </row>
-    <row r="65" ht="14.35" spans="1:5">
+    <row r="65" spans="1:5">
       <c r="A65" s="84" t="s">
         <v>121</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="66" ht="14.35" spans="1:5">
+    <row r="66" spans="1:5">
       <c r="A66" s="84" t="s">
         <v>124</v>
       </c>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E66" s="50"/>
     </row>
-    <row r="67" ht="14.35" spans="1:5">
+    <row r="67" spans="1:5">
       <c r="A67" s="84" t="s">
         <v>23</v>
       </c>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E67" s="50"/>
     </row>
-    <row r="68" ht="14.35" spans="1:5">
+    <row r="68" spans="1:5">
       <c r="A68" s="84" t="s">
         <v>125</v>
       </c>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E68" s="50"/>
     </row>
-    <row r="69" ht="14.35" spans="1:5">
+    <row r="69" spans="1:5">
       <c r="A69" s="84" t="s">
         <v>127</v>
       </c>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E69" s="50"/>
     </row>
-    <row r="70" ht="14.35" spans="1:5">
+    <row r="70" spans="1:5">
       <c r="A70" s="84" t="s">
         <v>43</v>
       </c>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="E70" s="50"/>
     </row>
-    <row r="71" ht="14.35" spans="1:5">
+    <row r="71" spans="1:5">
       <c r="A71" s="84" t="s">
         <v>129</v>
       </c>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E71" s="50"/>
     </row>
-    <row r="72" ht="14.35" spans="1:5">
+    <row r="72" spans="1:5">
       <c r="A72" s="84" t="s">
         <v>132</v>
       </c>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E72" s="50"/>
     </row>
-    <row r="73" ht="14.35" spans="1:5">
+    <row r="73" spans="1:5">
       <c r="A73" s="84" t="s">
         <v>135</v>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="E73" s="50"/>
     </row>
-    <row r="74" ht="14.35" spans="1:5">
+    <row r="74" spans="1:5">
       <c r="A74" s="84" t="s">
         <v>137</v>
       </c>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="E74" s="50"/>
     </row>
-    <row r="75" ht="14.35" spans="1:5">
+    <row r="75" spans="1:5">
       <c r="A75" s="84" t="s">
         <v>139</v>
       </c>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E75" s="50"/>
     </row>
-    <row r="76" ht="14.35" spans="1:5">
+    <row r="76" spans="1:5">
       <c r="A76" s="84" t="s">
         <v>141</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" ht="14.35" spans="1:5">
+    <row r="77" spans="1:5">
       <c r="A77" s="84" t="s">
         <v>143</v>
       </c>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="E77" s="38"/>
     </row>
-    <row r="78" ht="14.35" spans="1:5">
+    <row r="78" spans="1:5">
       <c r="A78" s="84" t="s">
         <v>145</v>
       </c>
@@ -3929,12 +3929,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="80" ht="17.65" spans="1:5">
+    <row r="80" ht="18.75" spans="1:5">
       <c r="A80" s="73" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="81" ht="14.35" spans="1:5">
+    <row r="81" spans="1:5">
       <c r="A81" s="64" t="s">
         <v>149</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" ht="14.35" spans="1:5">
+    <row r="82" spans="1:5">
       <c r="A82" s="91" t="s">
         <v>16</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" ht="14.35" spans="1:5">
+    <row r="83" spans="1:5">
       <c r="A83" s="91" t="s">
         <v>152</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" ht="14.35" spans="1:5">
+    <row r="84" spans="1:5">
       <c r="A84" s="91" t="s">
         <v>31</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" ht="14.35" spans="1:5">
+    <row r="85" spans="1:5">
       <c r="A85" s="91" t="s">
         <v>155</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" ht="14.35" spans="1:5">
+    <row r="86" spans="1:5">
       <c r="A86" s="91" t="s">
         <v>158</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" ht="14.35" spans="1:5">
+    <row r="87" spans="1:5">
       <c r="A87" s="91" t="s">
         <v>161</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" ht="14.35" spans="1:5">
+    <row r="88" spans="1:5">
       <c r="A88" s="91" t="s">
         <v>164</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" ht="14.35" spans="1:5">
+    <row r="89" spans="1:5">
       <c r="A89" s="91" t="s">
         <v>167</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" ht="14.35" spans="1:5">
+    <row r="90" spans="1:5">
       <c r="A90" s="91" t="s">
         <v>169</v>
       </c>
@@ -4077,15 +4077,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" ht="35.35" spans="1:5">
+    <row r="92" ht="37.5" spans="1:5">
       <c r="A92" s="92" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="93" ht="17.65" spans="1:5">
+    <row r="93" ht="18.75" spans="1:5">
       <c r="A93" s="93"/>
     </row>
-    <row r="94" ht="35.35" spans="1:5">
+    <row r="94" ht="37.5" spans="1:5">
       <c r="A94" s="94" t="s">
         <v>172</v>
       </c>
@@ -4103,19 +4103,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AL96"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" style="60" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="61" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" style="60" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" style="61" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" style="62" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" style="60" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="61" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" style="60" customWidth="1"/>
+    <col min="4" max="4" width="24.85" style="61" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" style="62" customWidth="1"/>
     <col min="6" max="6" width="9" style="48"/>
-    <col min="7" max="7" width="29.2035398230088" style="48" customWidth="1"/>
+    <col min="7" max="7" width="29.2" style="48" customWidth="1"/>
     <col min="8" max="16384" width="9" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:38">
+    <row r="1" ht="20.25" spans="1:38">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17.65" spans="1:38">
+    <row r="2" ht="18.75" spans="1:38">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" ht="14.35" spans="1:38">
+    <row r="3" spans="1:38">
       <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" ht="14.35" spans="1:38">
+    <row r="5" spans="1:38">
       <c r="A5" s="6" t="s">
         <v>72</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" ht="43" spans="1:38">
+    <row r="6" ht="40.5" spans="1:38">
       <c r="A6" s="45" t="s">
         <v>10</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="28.65" spans="1:38">
+    <row r="7" ht="27" spans="1:38">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="14.35" spans="1:38">
+    <row r="8" spans="1:38">
       <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="14.35" spans="1:38">
+    <row r="9" spans="1:38">
       <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="E9" s="53"/>
     </row>
-    <row r="10" ht="14.35" spans="1:38">
+    <row r="10" spans="1:38">
       <c r="A10" s="6" t="s">
         <v>31</v>
       </c>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E10" s="53"/>
     </row>
-    <row r="11" ht="14.35" spans="1:38">
+    <row r="11" spans="1:38">
       <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E11" s="53"/>
     </row>
-    <row r="12" ht="14.35" spans="1:38">
+    <row r="12" spans="1:38">
       <c r="A12" s="6" t="s">
         <v>180</v>
       </c>
@@ -4322,7 +4322,7 @@
       <c r="D13" s="21"/>
       <c r="E13" s="53"/>
     </row>
-    <row r="14" ht="17.65" spans="1:38">
+    <row r="14" ht="18.75" spans="1:38">
       <c r="A14" s="33" t="s">
         <v>45</v>
       </c>
@@ -4331,7 +4331,7 @@
       <c r="D14" s="21"/>
       <c r="E14" s="53"/>
     </row>
-    <row r="15" ht="14.35" spans="1:38">
+    <row r="15" spans="1:38">
       <c r="A15" s="30" t="s">
         <v>46</v>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="AK15" s="70"/>
       <c r="AL15" s="70"/>
     </row>
-    <row r="16" ht="14.35" spans="1:38">
+    <row r="16" spans="1:38">
       <c r="A16" s="30" t="s">
         <v>23</v>
       </c>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="E16" s="53"/>
     </row>
-    <row r="17" ht="14.35" spans="1:5">
+    <row r="17" spans="1:5">
       <c r="A17" s="30" t="s">
         <v>6</v>
       </c>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="E17" s="53"/>
     </row>
-    <row r="18" ht="14.35" spans="1:5">
+    <row r="18" spans="1:5">
       <c r="A18" s="30" t="s">
         <v>26</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" ht="14.35" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" s="30" t="s">
         <v>50</v>
       </c>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E19" s="53"/>
     </row>
-    <row r="20" ht="14.35" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20" s="30" t="s">
         <v>75</v>
       </c>
@@ -4458,7 +4458,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" ht="14.35" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" s="30" t="s">
         <v>72</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" ht="14.35" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" s="30" t="s">
         <v>29</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="23" ht="14.35" spans="1:5">
+    <row r="23" spans="1:5">
       <c r="A23" s="30" t="s">
         <v>182</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="24" ht="14.35" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24" s="30" t="s">
         <v>185</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="25" ht="14.35" spans="1:5">
+    <row r="25" spans="1:5">
       <c r="A25" s="30" t="s">
         <v>43</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="26" ht="14.35" spans="1:5">
+    <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
         <v>180</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" ht="14.35" spans="1:5">
+    <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
         <v>188</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" ht="14.35" spans="1:5">
+    <row r="28" spans="1:5">
       <c r="A28" s="30" t="s">
         <v>189</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" ht="14.35" spans="1:5">
+    <row r="29" spans="1:5">
       <c r="A29" s="30" t="s">
         <v>192</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="30" ht="14.35" spans="1:5">
+    <row r="30" spans="1:5">
       <c r="A30" s="30" t="s">
         <v>195</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="31" ht="14.35" spans="1:5">
+    <row r="31" spans="1:5">
       <c r="A31" s="30" t="s">
         <v>108</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="32" ht="14.35" spans="1:5">
+    <row r="32" spans="1:5">
       <c r="A32" s="30" t="s">
         <v>54</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" ht="14.35" spans="1:5">
+    <row r="33" spans="1:5">
       <c r="A33" s="30" t="s">
         <v>198</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" ht="14.35" spans="1:5">
+    <row r="34" spans="1:5">
       <c r="A34" s="30" t="s">
         <v>200</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35" ht="14.35" spans="1:5">
+    <row r="35" spans="1:5">
       <c r="A35" s="30" t="s">
         <v>60</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" ht="14.35" spans="1:5">
+    <row r="36" spans="1:5">
       <c r="A36" s="30" t="s">
         <v>88</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="37" ht="14.35" spans="1:5">
+    <row r="37" spans="1:5">
       <c r="A37" s="30" t="s">
         <v>57</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" ht="14.35" spans="1:5">
+    <row r="38" spans="1:5">
       <c r="A38" s="30" t="s">
         <v>202</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" ht="14.35" spans="1:5">
+    <row r="39" spans="1:5">
       <c r="A39" s="30" t="s">
         <v>204</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" ht="14.35" spans="1:5">
+    <row r="40" spans="1:5">
       <c r="A40" s="30" t="s">
         <v>64</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" ht="14.35" spans="1:5">
+    <row r="41" spans="1:5">
       <c r="A41" s="30" t="s">
         <v>4</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="42" ht="14.35" spans="1:5">
+    <row r="42" spans="1:5">
       <c r="A42" s="30" t="s">
         <v>124</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" ht="14.35" spans="1:5">
+    <row r="43" spans="1:5">
       <c r="A43" s="30" t="s">
         <v>70</v>
       </c>
@@ -4798,7 +4798,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="44" ht="28.65" spans="1:5">
+    <row r="44" ht="27" spans="1:5">
       <c r="A44" s="30" t="s">
         <v>208</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="45" ht="28.65" spans="1:5">
+    <row r="45" ht="27" spans="1:5">
       <c r="A45" s="30" t="s">
         <v>212</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="46" ht="28.65" spans="1:5">
+    <row r="46" ht="27" spans="1:5">
       <c r="A46" s="30" t="s">
         <v>215</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" ht="28.65" spans="1:5">
+    <row r="47" ht="27" spans="1:5">
       <c r="A47" s="30" t="s">
         <v>220</v>
       </c>
@@ -4860,12 +4860,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="49" ht="17.65" spans="1:5">
+    <row r="49" ht="18.75" spans="1:5">
       <c r="A49" s="33" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="50" ht="14.35" spans="1:5">
+    <row r="50" spans="1:5">
       <c r="A50" s="7" t="s">
         <v>50</v>
       </c>
@@ -4879,7 +4879,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="51" ht="14.35" spans="1:5">
+    <row r="51" spans="1:5">
       <c r="A51" s="7" t="s">
         <v>6</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" ht="14.35" spans="1:5">
+    <row r="52" spans="1:5">
       <c r="A52" s="7" t="s">
         <v>23</v>
       </c>
@@ -4907,7 +4907,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" ht="14.35" spans="1:5">
+    <row r="53" spans="1:5">
       <c r="A53" s="7" t="s">
         <v>72</v>
       </c>
@@ -4938,7 +4938,7 @@
       <c r="B55" s="21"/>
       <c r="C55" s="22"/>
     </row>
-    <row r="56" ht="14.35" spans="1:5">
+    <row r="56" spans="1:5">
       <c r="A56" s="7" t="s">
         <v>75</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" ht="14.35" spans="1:5">
+    <row r="57" spans="1:5">
       <c r="A57" s="7" t="s">
         <v>29</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="58" ht="14.35" spans="1:5">
+    <row r="58" spans="1:5">
       <c r="A58" s="9" t="s">
         <v>34</v>
       </c>
@@ -4986,7 +4986,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" ht="14.35" spans="1:5">
+    <row r="59" spans="1:5">
       <c r="A59" s="7" t="s">
         <v>185</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="60" ht="14.35" spans="1:5">
+    <row r="60" spans="1:5">
       <c r="A60" s="7" t="s">
         <v>188</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" ht="14.35" spans="1:5">
+    <row r="61" spans="1:5">
       <c r="A61" s="7" t="s">
         <v>180</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" ht="14.35" spans="1:5">
+    <row r="62" spans="1:5">
       <c r="A62" s="7" t="s">
         <v>189</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" ht="14.35" spans="1:5">
+    <row r="63" spans="1:5">
       <c r="A63" s="7" t="s">
         <v>43</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="64" ht="14.35" spans="1:5">
+    <row r="64" spans="1:5">
       <c r="A64" s="7" t="s">
         <v>192</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" ht="14.35" spans="1:5">
+    <row r="65" spans="1:5">
       <c r="A65" s="7" t="s">
         <v>195</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" ht="14.35" spans="1:5">
+    <row r="66" spans="1:5">
       <c r="A66" s="7" t="s">
         <v>88</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="67" ht="14.35" spans="1:5">
+    <row r="67" spans="1:5">
       <c r="A67" s="7" t="s">
         <v>108</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" ht="14.35" spans="1:5">
+    <row r="68" spans="1:5">
       <c r="A68" s="7" t="s">
         <v>57</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="69" ht="14.35" spans="1:5">
+    <row r="69" spans="1:5">
       <c r="A69" s="7" t="s">
         <v>54</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="70" ht="14.35" spans="1:5">
+    <row r="70" spans="1:5">
       <c r="A70" s="7" t="s">
         <v>202</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="71" ht="14.35" spans="1:5">
+    <row r="71" spans="1:5">
       <c r="A71" s="7" t="s">
         <v>198</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="72" ht="14.35" spans="1:5">
+    <row r="72" spans="1:5">
       <c r="A72" s="7" t="s">
         <v>204</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="73" ht="14.35" spans="1:5">
+    <row r="73" spans="1:5">
       <c r="A73" s="7" t="s">
         <v>200</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="74" ht="14.35" spans="1:5">
+    <row r="74" spans="1:5">
       <c r="A74" s="7" t="s">
         <v>64</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" ht="14.35" spans="1:5">
+    <row r="75" spans="1:5">
       <c r="A75" s="7" t="s">
         <v>60</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" ht="14.35" spans="1:5">
+    <row r="76" spans="1:5">
       <c r="A76" s="7" t="s">
         <v>26</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" ht="14.35" spans="1:5">
+    <row r="77" spans="1:5">
       <c r="A77" s="7" t="s">
         <v>70</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="78" ht="14.35" spans="1:5">
+    <row r="78" spans="1:5">
       <c r="A78" s="7" t="s">
         <v>124</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="79" ht="14.35" spans="1:5">
+    <row r="79" spans="1:5">
       <c r="A79" s="7" t="s">
         <v>4</v>
       </c>
@@ -5298,12 +5298,12 @@
     <row r="80" spans="1:5">
       <c r="A80" s="7"/>
     </row>
-    <row r="81" ht="17.65" spans="1:5">
+    <row r="81" ht="18.75" spans="1:5">
       <c r="A81" s="33" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="82" ht="14.35" spans="1:5">
+    <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
         <v>23</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" ht="14.35" spans="1:5">
+    <row r="84" spans="1:5">
       <c r="A84" s="30" t="s">
         <v>16</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" ht="14.35" spans="1:5">
+    <row r="85" spans="1:5">
       <c r="A85" s="30" t="s">
         <v>31</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" ht="14.35" spans="1:5">
+    <row r="86" spans="1:5">
       <c r="A86" s="30" t="s">
         <v>152</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" ht="14.35" spans="1:5">
+    <row r="87" spans="1:5">
       <c r="A87" s="30" t="s">
         <v>155</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" ht="14.35" spans="1:5">
+    <row r="88" spans="1:5">
       <c r="A88" s="30" t="s">
         <v>158</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" ht="14.35" spans="1:5">
+    <row r="89" spans="1:5">
       <c r="A89" s="30" t="s">
         <v>161</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" ht="14.35" spans="1:5">
+    <row r="90" spans="1:5">
       <c r="A90" s="30" t="s">
         <v>164</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" ht="14.35" spans="1:5">
+    <row r="91" spans="1:5">
       <c r="A91" s="30" t="s">
         <v>167</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" ht="14.35" spans="1:5">
+    <row r="92" spans="1:5">
       <c r="A92" s="30" t="s">
         <v>169</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" ht="14.35" spans="1:5">
+    <row r="93" spans="1:5">
       <c r="A93" s="30" t="s">
         <v>149</v>
       </c>
@@ -5473,7 +5473,7 @@
       <c r="C94" s="9"/>
       <c r="D94" s="29"/>
     </row>
-    <row r="95" ht="14.35" spans="1:5">
+    <row r="95" spans="1:5">
       <c r="A95" s="30" t="s">
         <v>124</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" ht="14.35" spans="1:5">
+    <row r="96" spans="1:5">
       <c r="A96" s="30" t="s">
         <v>70</v>
       </c>
@@ -5516,18 +5516,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
-    <col min="7" max="7" width="29.2035398230088" customWidth="1"/>
-    <col min="9" max="9" width="29.2035398230088" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" customWidth="1"/>
+    <col min="4" max="4" width="24.85" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" customWidth="1"/>
+    <col min="7" max="7" width="29.2" customWidth="1"/>
+    <col min="9" max="9" width="29.2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:7">
+    <row r="1" ht="20.25" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17.65" spans="1:7">
+    <row r="2" ht="18.75" spans="1:7">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" ht="14.35" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" ht="14.35" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>72</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" ht="43" spans="1:7">
+    <row r="6" ht="40.5" spans="1:7">
       <c r="A6" s="18" t="s">
         <v>10</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" ht="28.65" spans="1:7">
+    <row r="7" ht="27" spans="1:7">
       <c r="A7" s="18" t="s">
         <v>14</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="14.35" spans="1:7">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="14.35" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E9" s="41"/>
     </row>
-    <row r="10" ht="14.35" spans="1:7">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="E10" s="41"/>
     </row>
-    <row r="11" ht="14.35" spans="1:7">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="E11" s="41"/>
     </row>
-    <row r="12" ht="14.35" spans="1:7">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="E12" s="34"/>
     </row>
-    <row r="13" ht="14.35" spans="1:7">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -5748,7 +5748,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="34"/>
     </row>
-    <row r="15" ht="17.65" spans="1:7">
+    <row r="15" ht="18.75" spans="1:7">
       <c r="A15" s="33" t="s">
         <v>45</v>
       </c>
@@ -5757,7 +5757,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="34"/>
     </row>
-    <row r="16" ht="14.35" spans="1:7">
+    <row r="16" spans="1:7">
       <c r="A16" s="30" t="s">
         <v>46</v>
       </c>
@@ -5774,7 +5774,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="46"/>
     </row>
-    <row r="17" ht="14.35" spans="1:7">
+    <row r="17" spans="1:7">
       <c r="A17" s="30" t="s">
         <v>23</v>
       </c>
@@ -5791,7 +5791,7 @@
       <c r="F17" s="22"/>
       <c r="G17" s="47"/>
     </row>
-    <row r="18" ht="14.35" spans="1:7">
+    <row r="18" spans="1:7">
       <c r="A18" s="30" t="s">
         <v>6</v>
       </c>
@@ -5808,7 +5808,7 @@
       <c r="F18" s="22"/>
       <c r="G18" s="47"/>
     </row>
-    <row r="19" ht="14.35" spans="1:7">
+    <row r="19" spans="1:7">
       <c r="A19" s="30" t="s">
         <v>26</v>
       </c>
@@ -5827,7 +5827,7 @@
       <c r="F19" s="22"/>
       <c r="G19" s="47"/>
     </row>
-    <row r="20" ht="14.35" spans="1:7">
+    <row r="20" spans="1:7">
       <c r="A20" s="30" t="s">
         <v>50</v>
       </c>
@@ -5844,7 +5844,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="47"/>
     </row>
-    <row r="21" ht="14.35" spans="1:7">
+    <row r="21" spans="1:7">
       <c r="A21" s="30" t="s">
         <v>75</v>
       </c>
@@ -5863,7 +5863,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="47"/>
     </row>
-    <row r="22" ht="14.35" spans="1:7">
+    <row r="22" spans="1:7">
       <c r="A22" s="30" t="s">
         <v>72</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="F22" s="22"/>
       <c r="G22" s="47"/>
     </row>
-    <row r="23" ht="14.35" spans="1:7">
+    <row r="23" spans="1:7">
       <c r="A23" s="30" t="s">
         <v>29</v>
       </c>
@@ -5899,7 +5899,7 @@
       <c r="F23" s="22"/>
       <c r="G23" s="47"/>
     </row>
-    <row r="24" ht="14.35" spans="1:7">
+    <row r="24" spans="1:7">
       <c r="A24" s="30" t="s">
         <v>182</v>
       </c>
@@ -5918,7 +5918,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="47"/>
     </row>
-    <row r="25" ht="14.35" spans="1:7">
+    <row r="25" spans="1:7">
       <c r="A25" s="30" t="s">
         <v>185</v>
       </c>
@@ -5937,7 +5937,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="47"/>
     </row>
-    <row r="26" ht="14.35" spans="1:7">
+    <row r="26" spans="1:7">
       <c r="A26" s="30" t="s">
         <v>81</v>
       </c>
@@ -5956,7 +5956,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="47"/>
     </row>
-    <row r="27" ht="14.35" spans="1:7">
+    <row r="27" spans="1:7">
       <c r="A27" s="30" t="s">
         <v>37</v>
       </c>
@@ -5973,7 +5973,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="47"/>
     </row>
-    <row r="28" ht="14.35" spans="1:7">
+    <row r="28" spans="1:7">
       <c r="A28" s="30" t="s">
         <v>129</v>
       </c>
@@ -5990,7 +5990,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="47"/>
     </row>
-    <row r="29" ht="14.35" spans="1:7">
+    <row r="29" spans="1:7">
       <c r="A29" s="30" t="s">
         <v>84</v>
       </c>
@@ -6009,7 +6009,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="47"/>
     </row>
-    <row r="30" ht="14.35" spans="1:7">
+    <row r="30" spans="1:7">
       <c r="A30" s="30" t="s">
         <v>40</v>
       </c>
@@ -6026,7 +6026,7 @@
       <c r="F30" s="6"/>
       <c r="G30" s="47"/>
     </row>
-    <row r="31" ht="14.35" spans="1:7">
+    <row r="31" spans="1:7">
       <c r="A31" s="30" t="s">
         <v>132</v>
       </c>
@@ -6043,7 +6043,7 @@
       <c r="F31" s="6"/>
       <c r="G31" s="47"/>
     </row>
-    <row r="32" ht="14.35" spans="1:7">
+    <row r="32" spans="1:7">
       <c r="A32" s="30" t="s">
         <v>43</v>
       </c>
@@ -6060,7 +6060,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="47"/>
     </row>
-    <row r="33" ht="14.35" spans="1:7">
+    <row r="33" spans="1:7">
       <c r="A33" s="30" t="s">
         <v>192</v>
       </c>
@@ -6077,7 +6077,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="47"/>
     </row>
-    <row r="34" ht="14.35" spans="1:7">
+    <row r="34" spans="1:7">
       <c r="A34" s="30" t="s">
         <v>228</v>
       </c>
@@ -6094,7 +6094,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="47"/>
     </row>
-    <row r="35" ht="14.35" spans="1:7">
+    <row r="35" spans="1:7">
       <c r="A35" s="30" t="s">
         <v>230</v>
       </c>
@@ -6111,7 +6111,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="47"/>
     </row>
-    <row r="36" ht="14.35" spans="1:7">
+    <row r="36" spans="1:7">
       <c r="A36" s="30" t="s">
         <v>233</v>
       </c>
@@ -6128,7 +6128,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="50"/>
     </row>
-    <row r="37" ht="14.35" spans="1:7">
+    <row r="37" spans="1:7">
       <c r="A37" s="30" t="s">
         <v>234</v>
       </c>
@@ -6145,7 +6145,7 @@
       <c r="F37" s="22"/>
       <c r="G37" s="47"/>
     </row>
-    <row r="38" ht="14.35" spans="1:7">
+    <row r="38" spans="1:7">
       <c r="A38" s="30" t="s">
         <v>235</v>
       </c>
@@ -6162,7 +6162,7 @@
       <c r="F38" s="22"/>
       <c r="G38" s="47"/>
     </row>
-    <row r="39" ht="14.35" spans="1:7">
+    <row r="39" spans="1:7">
       <c r="A39" s="30" t="s">
         <v>236</v>
       </c>
@@ -6179,7 +6179,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="47"/>
     </row>
-    <row r="40" ht="14.35" spans="1:7">
+    <row r="40" spans="1:7">
       <c r="A40" s="30" t="s">
         <v>237</v>
       </c>
@@ -6198,7 +6198,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="47"/>
     </row>
-    <row r="41" ht="14.35" spans="1:7">
+    <row r="41" spans="1:7">
       <c r="A41" s="30" t="s">
         <v>238</v>
       </c>
@@ -6215,7 +6215,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="50"/>
     </row>
-    <row r="42" ht="14.35" spans="1:7">
+    <row r="42" spans="1:7">
       <c r="A42" s="30" t="s">
         <v>239</v>
       </c>
@@ -6232,7 +6232,7 @@
       <c r="F42" s="22"/>
       <c r="G42" s="47"/>
     </row>
-    <row r="43" ht="14.35" spans="1:7">
+    <row r="43" spans="1:7">
       <c r="A43" s="30" t="s">
         <v>240</v>
       </c>
@@ -6249,7 +6249,7 @@
       <c r="F43" s="22"/>
       <c r="G43" s="47"/>
     </row>
-    <row r="44" ht="14.35" spans="1:7">
+    <row r="44" spans="1:7">
       <c r="A44" s="30" t="s">
         <v>241</v>
       </c>
@@ -6266,7 +6266,7 @@
       <c r="F44" s="9"/>
       <c r="G44" s="47"/>
     </row>
-    <row r="45" ht="14.35" spans="1:7">
+    <row r="45" spans="1:7">
       <c r="A45" s="30" t="s">
         <v>242</v>
       </c>
@@ -6285,7 +6285,7 @@
       <c r="F45" s="9"/>
       <c r="G45" s="47"/>
     </row>
-    <row r="46" ht="14.35" spans="1:7">
+    <row r="46" spans="1:7">
       <c r="A46" s="30" t="s">
         <v>4</v>
       </c>
@@ -6302,7 +6302,7 @@
       <c r="F46" s="52"/>
       <c r="G46" s="47"/>
     </row>
-    <row r="47" ht="14.35" spans="1:7">
+    <row r="47" spans="1:7">
       <c r="A47" s="30" t="s">
         <v>124</v>
       </c>
@@ -6319,7 +6319,7 @@
       <c r="F47" s="52"/>
       <c r="G47" s="47"/>
     </row>
-    <row r="48" ht="14.35" spans="1:7">
+    <row r="48" spans="1:7">
       <c r="A48" s="30" t="s">
         <v>70</v>
       </c>
@@ -6336,7 +6336,7 @@
       <c r="F48" s="52"/>
       <c r="G48" s="47"/>
     </row>
-    <row r="49" ht="28.65" spans="1:7">
+    <row r="49" ht="27" spans="1:7">
       <c r="A49" s="30" t="s">
         <v>208</v>
       </c>
@@ -6353,7 +6353,7 @@
       <c r="F49" s="52"/>
       <c r="G49" s="47"/>
     </row>
-    <row r="50" ht="28.65" spans="1:7">
+    <row r="50" ht="27" spans="1:7">
       <c r="A50" s="30" t="s">
         <v>212</v>
       </c>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="E50" s="41"/>
     </row>
-    <row r="51" ht="28.65" spans="1:7">
+    <row r="51" ht="27" spans="1:7">
       <c r="A51" s="30" t="s">
         <v>215</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="52" ht="28.65" spans="1:7">
+    <row r="52" ht="27" spans="1:7">
       <c r="A52" s="30" t="s">
         <v>220</v>
       </c>
@@ -6408,7 +6408,7 @@
       <c r="D53" s="10"/>
       <c r="E53" s="34"/>
     </row>
-    <row r="54" ht="17.65" spans="1:7">
+    <row r="54" ht="18.75" spans="1:7">
       <c r="A54" s="33" t="s">
         <v>224</v>
       </c>
@@ -6417,7 +6417,7 @@
       <c r="D54" s="10"/>
       <c r="E54" s="34"/>
     </row>
-    <row r="55" ht="14.35" spans="1:7">
+    <row r="55" spans="1:7">
       <c r="A55" s="1" t="s">
         <v>50</v>
       </c>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="E55" s="41"/>
     </row>
-    <row r="56" ht="14.35" spans="1:7">
+    <row r="56" spans="1:7">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E56" s="41"/>
     </row>
-    <row r="57" ht="14.35" spans="1:7">
+    <row r="57" spans="1:7">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="E57" s="41"/>
     </row>
-    <row r="58" ht="14.35" spans="1:7">
+    <row r="58" spans="1:7">
       <c r="A58" s="1" t="s">
         <v>72</v>
       </c>
@@ -6497,7 +6497,7 @@
       <c r="D60" s="54"/>
       <c r="E60" s="41"/>
     </row>
-    <row r="61" ht="14.35" spans="1:7">
+    <row r="61" spans="1:7">
       <c r="A61" s="1" t="s">
         <v>75</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" ht="14.35" spans="1:7">
+    <row r="62" spans="1:7">
       <c r="A62" s="1" t="s">
         <v>29</v>
       </c>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="E62" s="56"/>
     </row>
-    <row r="63" ht="14.35" spans="1:7">
+    <row r="63" spans="1:7">
       <c r="A63" s="18" t="s">
         <v>34</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="64" ht="14.35" spans="1:7">
+    <row r="64" spans="1:7">
       <c r="A64" s="1" t="s">
         <v>48</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="65" ht="14.35" spans="1:5">
+    <row r="65" spans="1:5">
       <c r="A65" s="1" t="s">
         <v>185</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="66" ht="14.35" spans="1:5">
+    <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>81</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" ht="14.35" spans="1:5">
+    <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
         <v>37</v>
       </c>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="E67" s="56"/>
     </row>
-    <row r="68" ht="14.35" spans="1:5">
+    <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
         <v>129</v>
       </c>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="E68" s="56"/>
     </row>
-    <row r="69" ht="14.35" spans="1:5">
+    <row r="69" spans="1:5">
       <c r="A69" s="1" t="s">
         <v>84</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="70" ht="14.35" spans="1:5">
+    <row r="70" spans="1:5">
       <c r="A70" s="1" t="s">
         <v>40</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="E70" s="56"/>
     </row>
-    <row r="71" ht="14.35" spans="1:5">
+    <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
         <v>132</v>
       </c>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="E71" s="56"/>
     </row>
-    <row r="72" ht="14.35" spans="1:5">
+    <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
         <v>43</v>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E72" s="56"/>
     </row>
-    <row r="73" ht="14.35" spans="1:5">
+    <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
         <v>192</v>
       </c>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="E73" s="56"/>
     </row>
-    <row r="74" ht="14.35" spans="1:5">
+    <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
         <v>228</v>
       </c>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="E74" s="56"/>
     </row>
-    <row r="75" ht="14.35" spans="1:5">
+    <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
         <v>230</v>
       </c>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="E75" s="56"/>
     </row>
-    <row r="76" ht="14.35" spans="1:5">
+    <row r="76" spans="1:5">
       <c r="A76" s="1" t="s">
         <v>238</v>
       </c>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="E76" s="56"/>
     </row>
-    <row r="77" ht="14.35" spans="1:5">
+    <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
         <v>233</v>
       </c>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="E77" s="56"/>
     </row>
-    <row r="78" ht="14.35" spans="1:5">
+    <row r="78" spans="1:5">
       <c r="A78" s="1" t="s">
         <v>239</v>
       </c>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="E78" s="56"/>
     </row>
-    <row r="79" ht="14.35" spans="1:5">
+    <row r="79" spans="1:5">
       <c r="A79" s="1" t="s">
         <v>234</v>
       </c>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="E79" s="56"/>
     </row>
-    <row r="80" ht="14.35" spans="1:5">
+    <row r="80" spans="1:5">
       <c r="A80" s="1" t="s">
         <v>240</v>
       </c>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="E80" s="56"/>
     </row>
-    <row r="81" ht="14.35" spans="1:5">
+    <row r="81" spans="1:5">
       <c r="A81" s="1" t="s">
         <v>235</v>
       </c>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="E81" s="56"/>
     </row>
-    <row r="82" ht="14.35" spans="1:5">
+    <row r="82" spans="1:5">
       <c r="A82" s="1" t="s">
         <v>241</v>
       </c>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="E82" s="56"/>
     </row>
-    <row r="83" ht="14.35" spans="1:5">
+    <row r="83" spans="1:5">
       <c r="A83" s="1" t="s">
         <v>236</v>
       </c>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E83" s="56"/>
     </row>
-    <row r="84" ht="14.35" spans="1:5">
+    <row r="84" spans="1:5">
       <c r="A84" s="1" t="s">
         <v>242</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" ht="14.35" spans="1:5">
+    <row r="85" spans="1:5">
       <c r="A85" s="1" t="s">
         <v>237</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" ht="14.35" spans="1:5">
+    <row r="86" spans="1:5">
       <c r="A86" s="1" t="s">
         <v>26</v>
       </c>
@@ -6905,7 +6905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" ht="14.35" spans="1:5">
+    <row r="87" spans="1:5">
       <c r="A87" s="1" t="s">
         <v>70</v>
       </c>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E87" s="34"/>
     </row>
-    <row r="88" ht="14.35" spans="1:5">
+    <row r="88" spans="1:5">
       <c r="A88" s="1" t="s">
         <v>124</v>
       </c>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="E88" s="34"/>
     </row>
-    <row r="89" ht="14.35" spans="1:5">
+    <row r="89" spans="1:5">
       <c r="A89" s="1" t="s">
         <v>4</v>
       </c>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="E89" s="34"/>
     </row>
-    <row r="91" ht="17.65" spans="1:5">
+    <row r="91" ht="18.75" spans="1:5">
       <c r="A91" s="33" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="92" ht="14.35" spans="1:5">
+    <row r="92" spans="1:5">
       <c r="A92" s="45" t="s">
         <v>23</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="94" ht="14.35" spans="1:5">
+    <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
         <v>16</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" ht="14.35" spans="1:5">
+    <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
         <v>31</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" ht="14.35" spans="1:5">
+    <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
         <v>152</v>
       </c>
@@ -7016,7 +7016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" ht="14.35" spans="1:5">
+    <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
         <v>155</v>
       </c>
@@ -7030,7 +7030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" ht="14.35" spans="1:5">
+    <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
         <v>158</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" ht="14.35" spans="1:5">
+    <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
         <v>161</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" ht="14.35" spans="1:5">
+    <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
         <v>164</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" ht="14.35" spans="1:5">
+    <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
         <v>167</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" ht="14.35" spans="1:5">
+    <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
         <v>169</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" ht="14.35" spans="1:5">
+    <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
         <v>149</v>
       </c>
@@ -7125,7 +7125,7 @@
       <c r="C104" s="7"/>
       <c r="D104" s="29"/>
     </row>
-    <row r="105" ht="14.35" spans="1:5">
+    <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
         <v>124</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" ht="14.35" spans="1:5">
+    <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
         <v>70</v>
       </c>
@@ -7232,16 +7232,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:5">
+    <row r="1" ht="20.25" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7258,14 +7258,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17.65" spans="1:5">
+    <row r="2" ht="18.75" spans="1:5">
       <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
     </row>
-    <row r="3" ht="14.35" spans="1:5">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>245</v>
       </c>
@@ -7371,7 +7371,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" ht="17.65" spans="1:5">
+    <row r="11" ht="18.75" spans="1:5">
       <c r="A11" s="33" t="s">
         <v>45</v>
       </c>
@@ -7379,7 +7379,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" ht="14.35" spans="1:5">
+    <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
         <v>247</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" ht="14.35" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
         <v>124</v>
       </c>
@@ -7525,7 +7525,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="22" ht="14.35" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
         <v>70</v>
       </c>
@@ -7549,16 +7549,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:5">
+    <row r="1" ht="20.25" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17.65" spans="1:5">
+    <row r="2" ht="18.75" spans="1:5">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -7594,7 +7594,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="4" ht="14.35" spans="1:5">
+    <row r="4" spans="1:5">
       <c r="A4" s="22" t="s">
         <v>16</v>
       </c>
@@ -7636,7 +7636,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="7" ht="14.35" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7" s="22" t="s">
         <v>245</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="10" ht="17.65" spans="1:5">
+    <row r="10" ht="18.75" spans="1:5">
       <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="12" ht="14.35" spans="1:5">
+    <row r="12" spans="1:5">
       <c r="A12" s="30" t="s">
         <v>277</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" ht="14.35" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="17" ht="14.35" spans="1:4">
+    <row r="17" spans="1:4">
       <c r="A17" s="6" t="s">
         <v>280</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" ht="14.35" spans="1:4">
+    <row r="27" spans="1:4">
       <c r="A27" s="6" t="s">
         <v>302</v>
       </c>
@@ -7937,22 +7937,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="13" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" style="13" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" style="13" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" style="14" customWidth="1"/>
-    <col min="6" max="6" width="42.141592920354" style="13" customWidth="1"/>
-    <col min="7" max="7" width="27.3097345132743" style="13" customWidth="1"/>
-    <col min="8" max="8" width="24.8495575221239" style="13" customWidth="1"/>
-    <col min="9" max="9" width="37.0088495575221" style="15" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="13" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.85" style="13" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" style="14" customWidth="1"/>
+    <col min="6" max="6" width="42.1416666666667" style="13" customWidth="1"/>
+    <col min="7" max="7" width="27.3083333333333" style="13" customWidth="1"/>
+    <col min="8" max="8" width="24.85" style="13" customWidth="1"/>
+    <col min="9" max="9" width="37.0083333333333" style="15" customWidth="1"/>
     <col min="10" max="10" width="9" style="15"/>
-    <col min="11" max="11" width="29.2035398230088" style="15" customWidth="1"/>
+    <col min="11" max="11" width="29.2" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:11">
+    <row r="1" ht="20.25" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7983,7 +7983,7 @@
       <c r="J1"/>
       <c r="K1"/>
     </row>
-    <row r="2" ht="17.65" spans="1:11">
+    <row r="2" ht="18.75" spans="1:11">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="K2" s="17"/>
     </row>
-    <row r="3" ht="14.35" spans="1:11">
+    <row r="3" spans="1:11">
       <c r="A3" s="18" t="s">
         <v>16</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="5" ht="14.35" spans="1:11">
+    <row r="5" spans="1:11">
       <c r="A5" s="18" t="s">
         <v>245</v>
       </c>
@@ -8070,7 +8070,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="6" ht="28.65" spans="1:11">
+    <row r="6" ht="27" spans="1:11">
       <c r="A6" s="18" t="s">
         <v>274</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="12" ht="17.65" spans="1:11">
+    <row r="12" ht="18.75" spans="1:11">
       <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" ht="14.35" spans="1:11">
+    <row r="14" spans="1:11">
       <c r="A14" s="7" t="s">
         <v>245</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" ht="14.35" spans="1:11">
+    <row r="15" spans="1:11">
       <c r="A15" s="7" t="s">
         <v>334</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" ht="28.65" spans="1:9">
+    <row r="18" ht="27" spans="1:9">
       <c r="A18" s="7" t="s">
         <v>274</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="19" ht="14.35" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19" s="7" t="s">
         <v>16</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="26" ht="57.35" spans="1:9">
+    <row r="26" ht="54" spans="1:9">
       <c r="A26" s="7" t="s">
         <v>290</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="27" ht="28.65" spans="1:9">
+    <row r="27" ht="27" spans="1:9">
       <c r="A27" s="7" t="s">
         <v>296</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="28" ht="28.65" spans="1:9">
+    <row r="28" ht="27" spans="1:9">
       <c r="A28" s="7" t="s">
         <v>302</v>
       </c>
@@ -8548,16 +8548,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.3" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="44.2300884955752" style="1" customWidth="1"/>
-    <col min="2" max="2" width="42.141592920354" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.3097345132743" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.8495575221239" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.0088495575221" style="2" customWidth="1"/>
+    <col min="1" max="1" width="44.2333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="42.1416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.3083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.0083333333333" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.65" spans="1:5">
+    <row r="1" ht="20.25" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="17.65" spans="1:5">
+    <row r="2" ht="18.75" spans="1:5">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -8607,12 +8607,12 @@
         <v>364</v>
       </c>
     </row>
-    <row r="6" ht="17.65" spans="1:5">
+    <row r="6" ht="18.75" spans="1:5">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" ht="17.65" spans="1:5">
+    <row r="7" ht="18.75" spans="1:5">
       <c r="A7" s="5"/>
       <c r="B7" s="1" t="s">
         <v>47</v>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" ht="14.35" spans="1:5">
+    <row r="9" spans="1:5">
       <c r="A9" s="6" t="s">
         <v>367</v>
       </c>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" ht="14.35" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" s="6" t="s">
         <v>375</v>
       </c>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" ht="57.35" spans="1:5">
+    <row r="15" ht="54" spans="1:5">
       <c r="A15" s="6" t="s">
         <v>377</v>
       </c>
@@ -8740,12 +8740,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="17" ht="17.65" spans="1:5">
+    <row r="17" ht="18.75" spans="1:5">
       <c r="A17" s="12" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="18" ht="14.35" spans="1:5">
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>380</v>
       </c>
@@ -8756,7 +8756,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="19" ht="14.35" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>382</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="21" ht="14.35" spans="1:5">
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>385</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="22" ht="14.35" spans="1:5">
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>386</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="23" ht="43" spans="1:5">
+    <row r="23" ht="40.5" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>388</v>
       </c>
@@ -8811,7 +8811,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="24" ht="14.35" spans="1:5">
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>390</v>
       </c>
